--- a/01-Projects/하루보고 홍보/월말 결산 양식 (무료배포).xlsx
+++ b/01-Projects/하루보고 홍보/월말 결산 양식 (무료배포).xlsx
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="112" customWidth="1" min="1" max="1"/>
@@ -711,40 +711,78 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>■ 주의</t>
+          <t>■ 제조원가 / 판관비 구분 (같은 계정명이 양쪽에 있을 때)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>· 같은 계정을 어떤 행은 코드로, 어떤 행은 이름만으로 쓰면 서로 다른 계정으로 집계됩니다.</t>
+          <t>· 복리후생비·감가상각비처럼 제조(5xx)와 판관(8xx)에 같은 이름이 있으면 코드로 자동 구분됩니다:</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  회계 프로그램에서 출력한 원장은 보통 형식이 일정하니 그대로 붙여넣으면 됩니다.</t>
+          <t xml:space="preserve">  코드 첫 자리 5=제조, 6=도급, 7=분양, 8=판관 → 명세서에 '복리후생비 (제)' / '복리후생비 (판)'으로 표시.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>· 노란색 칸 = 직접 입력   · 검은 글씨 = 자동 계산 (수정 금지)   · 예시값은 전부 가상 데이터입니다.</t>
+          <t>· 회사 코드 체계가 표준과 다르면 [코드매핑]의 '구분(선택)'·'원가구분(선택)' 열에 코드별로 직접 지정하세요</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">  — 지정값이 자동 판별보다 우선합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>■ 주의</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>· 같은 계정을 어떤 행은 코드로, 어떤 행은 이름만으로 쓰면 서로 다른 계정으로 집계됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  회계 프로그램에서 출력한 원장은 보통 형식이 일정하니 그대로 붙여넣으면 됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>· 노란색 칸 = 직접 입력   · 검은 글씨 = 자동 계산 (수정 금지)   · 예시값은 전부 가상 데이터입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
           <t>· 예시 시연 2가지: ① 미지급금이 50,000원 어긋나 있고 [결산조정] 한 줄로 맞춰짐</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  ② 거래처코드 C001만 있는 행이 [수정사항]에 떠 있음 → [코드매핑]에 C001/국민카드를 넣으면 사라짐.</t>
         </is>
@@ -2492,27 +2530,29 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="n"/>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>51100</t>
+        </is>
+      </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>미지급금</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>C001</t>
-        </is>
-      </c>
+          <t>복리후생비</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="n"/>
       <c r="E35" s="7" t="n"/>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>거래처코드 시연 — 코드매핑에 C001을 추가해보세요</t>
-        </is>
-      </c>
-      <c r="G35" s="8" t="n"/>
+          <t>9월 공장 식대 (제조원가 시연)</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="n">
+        <v>120000</v>
+      </c>
       <c r="H35" s="8" t="n"/>
       <c r="I35" s="9">
         <f>IF($B35&lt;&gt;"",$B35&amp;"",IF($C35&lt;&gt;"",$C35,""))</f>
@@ -2544,14 +2584,32 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="n"/>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="10" t="n"/>
-      <c r="E36" s="10" t="n"/>
-      <c r="F36" s="10" t="n"/>
-      <c r="G36" s="11" t="n"/>
-      <c r="H36" s="11" t="n"/>
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>81100</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>복리후생비</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="n"/>
+      <c r="E36" s="7" t="n"/>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>9월 사무실 식대 (판관비 시연)</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="n">
+        <v>80000</v>
+      </c>
+      <c r="H36" s="8" t="n"/>
       <c r="I36" s="9">
         <f>IF($B36&lt;&gt;"",$B36&amp;"",IF($C36&lt;&gt;"",$C36,""))</f>
         <v/>
@@ -2582,14 +2640,30 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="n"/>
-      <c r="B37" s="10" t="n"/>
-      <c r="C37" s="10" t="n"/>
-      <c r="D37" s="10" t="n"/>
-      <c r="E37" s="10" t="n"/>
-      <c r="F37" s="10" t="n"/>
-      <c r="G37" s="11" t="n"/>
-      <c r="H37" s="11" t="n"/>
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>미지급금</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>거래처코드 시연 — 코드매핑에 C001을 추가해보세요</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="n"/>
+      <c r="H37" s="8" t="n"/>
       <c r="I37" s="9">
         <f>IF($B37&lt;&gt;"",$B37&amp;"",IF($C37&lt;&gt;"",$C37,""))</f>
         <v/>
@@ -8976,26 +9050,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D104"/>
+  <dimension ref="A1:F106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>코드 매핑 — 코드만 있는 행의 이름을 여기서 정의</t>
+          <t>코드 매핑 — 코드만 있는 행의 이름·분류를 여기서 정의</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>■ [수정사항]에 '미확인'이 뜨면 여기에 코드와 이름을 한 줄 추가하세요. 추가 즉시 해당 코드의 모든 행에 반영됩니다.</t>
+          <t>■ [수정사항]에 '미확인'이 뜨면 코드와 이름을 추가하세요 (즉시 전체 반영). E·F열은 선택: 비워두면 이름·코드 첫 자리로 자동 판별합니다.</t>
         </is>
       </c>
     </row>
@@ -9019,6 +9095,16 @@
       <c r="D4" s="6" t="inlineStr">
         <is>
           <t>거래처명</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>구분(선택)</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>원가구분(선택)</t>
         </is>
       </c>
     </row>
@@ -9027,600 +9113,808 @@
       <c r="B5" s="10" t="n"/>
       <c r="C5" s="10" t="n"/>
       <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="10" t="n"/>
       <c r="B6" s="10" t="n"/>
       <c r="C6" s="10" t="n"/>
       <c r="D6" s="10" t="n"/>
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="10" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="10" t="n"/>
       <c r="B7" s="10" t="n"/>
       <c r="C7" s="10" t="n"/>
       <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="10" t="n"/>
       <c r="B8" s="10" t="n"/>
       <c r="C8" s="10" t="n"/>
       <c r="D8" s="10" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="n"/>
       <c r="B9" s="10" t="n"/>
       <c r="C9" s="10" t="n"/>
       <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="n"/>
       <c r="B10" s="10" t="n"/>
       <c r="C10" s="10" t="n"/>
       <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="n"/>
       <c r="B11" s="10" t="n"/>
       <c r="C11" s="10" t="n"/>
       <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="10" t="n"/>
       <c r="B12" s="10" t="n"/>
       <c r="C12" s="10" t="n"/>
       <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="n"/>
       <c r="B13" s="10" t="n"/>
       <c r="C13" s="10" t="n"/>
       <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="10" t="n"/>
       <c r="B14" s="10" t="n"/>
       <c r="C14" s="10" t="n"/>
       <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="n"/>
       <c r="B15" s="10" t="n"/>
       <c r="C15" s="10" t="n"/>
       <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="n"/>
       <c r="B16" s="10" t="n"/>
       <c r="C16" s="10" t="n"/>
       <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="10" t="n"/>
       <c r="B17" s="10" t="n"/>
       <c r="C17" s="10" t="n"/>
       <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="10" t="n"/>
       <c r="B18" s="10" t="n"/>
       <c r="C18" s="10" t="n"/>
       <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="10" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="n"/>
       <c r="B19" s="10" t="n"/>
       <c r="C19" s="10" t="n"/>
       <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="10" t="n"/>
       <c r="B20" s="10" t="n"/>
       <c r="C20" s="10" t="n"/>
       <c r="D20" s="10" t="n"/>
+      <c r="E20" s="10" t="n"/>
+      <c r="F20" s="10" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="n"/>
       <c r="B21" s="10" t="n"/>
       <c r="C21" s="10" t="n"/>
       <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="n"/>
       <c r="B22" s="10" t="n"/>
       <c r="C22" s="10" t="n"/>
       <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="n"/>
       <c r="B23" s="10" t="n"/>
       <c r="C23" s="10" t="n"/>
       <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="n"/>
       <c r="B24" s="10" t="n"/>
       <c r="C24" s="10" t="n"/>
       <c r="D24" s="10" t="n"/>
+      <c r="E24" s="10" t="n"/>
+      <c r="F24" s="10" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="10" t="n"/>
       <c r="B25" s="10" t="n"/>
       <c r="C25" s="10" t="n"/>
       <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="10" t="n"/>
       <c r="B26" s="10" t="n"/>
       <c r="C26" s="10" t="n"/>
       <c r="D26" s="10" t="n"/>
+      <c r="E26" s="10" t="n"/>
+      <c r="F26" s="10" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="10" t="n"/>
       <c r="B27" s="10" t="n"/>
       <c r="C27" s="10" t="n"/>
       <c r="D27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="10" t="n"/>
       <c r="B28" s="10" t="n"/>
       <c r="C28" s="10" t="n"/>
       <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="10" t="n"/>
       <c r="B29" s="10" t="n"/>
       <c r="C29" s="10" t="n"/>
       <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="10" t="n"/>
       <c r="B30" s="10" t="n"/>
       <c r="C30" s="10" t="n"/>
       <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="10" t="n"/>
       <c r="B31" s="10" t="n"/>
       <c r="C31" s="10" t="n"/>
       <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="10" t="n"/>
       <c r="B32" s="10" t="n"/>
       <c r="C32" s="10" t="n"/>
       <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="10" t="n"/>
       <c r="B33" s="10" t="n"/>
       <c r="C33" s="10" t="n"/>
       <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="10" t="n"/>
       <c r="B34" s="10" t="n"/>
       <c r="C34" s="10" t="n"/>
       <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="10" t="n"/>
       <c r="B35" s="10" t="n"/>
       <c r="C35" s="10" t="n"/>
       <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="10" t="n"/>
       <c r="B36" s="10" t="n"/>
       <c r="C36" s="10" t="n"/>
       <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="10" t="n"/>
       <c r="B37" s="10" t="n"/>
       <c r="C37" s="10" t="n"/>
       <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="10" t="n"/>
       <c r="B38" s="10" t="n"/>
       <c r="C38" s="10" t="n"/>
       <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="10" t="n"/>
       <c r="B39" s="10" t="n"/>
       <c r="C39" s="10" t="n"/>
       <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="10" t="n"/>
       <c r="B40" s="10" t="n"/>
       <c r="C40" s="10" t="n"/>
       <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="10" t="n"/>
       <c r="B41" s="10" t="n"/>
       <c r="C41" s="10" t="n"/>
       <c r="D41" s="10" t="n"/>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="10" t="n"/>
       <c r="B42" s="10" t="n"/>
       <c r="C42" s="10" t="n"/>
       <c r="D42" s="10" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="10" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="10" t="n"/>
       <c r="B43" s="10" t="n"/>
       <c r="C43" s="10" t="n"/>
       <c r="D43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="10" t="n"/>
       <c r="B44" s="10" t="n"/>
       <c r="C44" s="10" t="n"/>
       <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="10" t="n"/>
       <c r="B45" s="10" t="n"/>
       <c r="C45" s="10" t="n"/>
       <c r="D45" s="10" t="n"/>
+      <c r="E45" s="10" t="n"/>
+      <c r="F45" s="10" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="10" t="n"/>
       <c r="B46" s="10" t="n"/>
       <c r="C46" s="10" t="n"/>
       <c r="D46" s="10" t="n"/>
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="10" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="10" t="n"/>
       <c r="B47" s="10" t="n"/>
       <c r="C47" s="10" t="n"/>
       <c r="D47" s="10" t="n"/>
+      <c r="E47" s="10" t="n"/>
+      <c r="F47" s="10" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="10" t="n"/>
       <c r="B48" s="10" t="n"/>
       <c r="C48" s="10" t="n"/>
       <c r="D48" s="10" t="n"/>
+      <c r="E48" s="10" t="n"/>
+      <c r="F48" s="10" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="10" t="n"/>
       <c r="B49" s="10" t="n"/>
       <c r="C49" s="10" t="n"/>
       <c r="D49" s="10" t="n"/>
+      <c r="E49" s="10" t="n"/>
+      <c r="F49" s="10" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="10" t="n"/>
       <c r="B50" s="10" t="n"/>
       <c r="C50" s="10" t="n"/>
       <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="10" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="10" t="n"/>
       <c r="B51" s="10" t="n"/>
       <c r="C51" s="10" t="n"/>
       <c r="D51" s="10" t="n"/>
+      <c r="E51" s="10" t="n"/>
+      <c r="F51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="10" t="n"/>
       <c r="B52" s="10" t="n"/>
       <c r="C52" s="10" t="n"/>
       <c r="D52" s="10" t="n"/>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="10" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="10" t="n"/>
       <c r="B53" s="10" t="n"/>
       <c r="C53" s="10" t="n"/>
       <c r="D53" s="10" t="n"/>
+      <c r="E53" s="10" t="n"/>
+      <c r="F53" s="10" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="10" t="n"/>
       <c r="B54" s="10" t="n"/>
       <c r="C54" s="10" t="n"/>
       <c r="D54" s="10" t="n"/>
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="10" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="10" t="n"/>
       <c r="B55" s="10" t="n"/>
       <c r="C55" s="10" t="n"/>
       <c r="D55" s="10" t="n"/>
+      <c r="E55" s="10" t="n"/>
+      <c r="F55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="10" t="n"/>
       <c r="B56" s="10" t="n"/>
       <c r="C56" s="10" t="n"/>
       <c r="D56" s="10" t="n"/>
+      <c r="E56" s="10" t="n"/>
+      <c r="F56" s="10" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="10" t="n"/>
       <c r="B57" s="10" t="n"/>
       <c r="C57" s="10" t="n"/>
       <c r="D57" s="10" t="n"/>
+      <c r="E57" s="10" t="n"/>
+      <c r="F57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="10" t="n"/>
       <c r="B58" s="10" t="n"/>
       <c r="C58" s="10" t="n"/>
       <c r="D58" s="10" t="n"/>
+      <c r="E58" s="10" t="n"/>
+      <c r="F58" s="10" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="10" t="n"/>
       <c r="B59" s="10" t="n"/>
       <c r="C59" s="10" t="n"/>
       <c r="D59" s="10" t="n"/>
+      <c r="E59" s="10" t="n"/>
+      <c r="F59" s="10" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="10" t="n"/>
       <c r="B60" s="10" t="n"/>
       <c r="C60" s="10" t="n"/>
       <c r="D60" s="10" t="n"/>
+      <c r="E60" s="10" t="n"/>
+      <c r="F60" s="10" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="10" t="n"/>
       <c r="B61" s="10" t="n"/>
       <c r="C61" s="10" t="n"/>
       <c r="D61" s="10" t="n"/>
+      <c r="E61" s="10" t="n"/>
+      <c r="F61" s="10" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="10" t="n"/>
       <c r="B62" s="10" t="n"/>
       <c r="C62" s="10" t="n"/>
       <c r="D62" s="10" t="n"/>
+      <c r="E62" s="10" t="n"/>
+      <c r="F62" s="10" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="10" t="n"/>
       <c r="B63" s="10" t="n"/>
       <c r="C63" s="10" t="n"/>
       <c r="D63" s="10" t="n"/>
+      <c r="E63" s="10" t="n"/>
+      <c r="F63" s="10" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="10" t="n"/>
       <c r="B64" s="10" t="n"/>
       <c r="C64" s="10" t="n"/>
       <c r="D64" s="10" t="n"/>
+      <c r="E64" s="10" t="n"/>
+      <c r="F64" s="10" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="10" t="n"/>
       <c r="B65" s="10" t="n"/>
       <c r="C65" s="10" t="n"/>
       <c r="D65" s="10" t="n"/>
+      <c r="E65" s="10" t="n"/>
+      <c r="F65" s="10" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="10" t="n"/>
       <c r="B66" s="10" t="n"/>
       <c r="C66" s="10" t="n"/>
       <c r="D66" s="10" t="n"/>
+      <c r="E66" s="10" t="n"/>
+      <c r="F66" s="10" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="10" t="n"/>
       <c r="B67" s="10" t="n"/>
       <c r="C67" s="10" t="n"/>
       <c r="D67" s="10" t="n"/>
+      <c r="E67" s="10" t="n"/>
+      <c r="F67" s="10" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="10" t="n"/>
       <c r="B68" s="10" t="n"/>
       <c r="C68" s="10" t="n"/>
       <c r="D68" s="10" t="n"/>
+      <c r="E68" s="10" t="n"/>
+      <c r="F68" s="10" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="10" t="n"/>
       <c r="B69" s="10" t="n"/>
       <c r="C69" s="10" t="n"/>
       <c r="D69" s="10" t="n"/>
+      <c r="E69" s="10" t="n"/>
+      <c r="F69" s="10" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="10" t="n"/>
       <c r="B70" s="10" t="n"/>
       <c r="C70" s="10" t="n"/>
       <c r="D70" s="10" t="n"/>
+      <c r="E70" s="10" t="n"/>
+      <c r="F70" s="10" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="10" t="n"/>
       <c r="B71" s="10" t="n"/>
       <c r="C71" s="10" t="n"/>
       <c r="D71" s="10" t="n"/>
+      <c r="E71" s="10" t="n"/>
+      <c r="F71" s="10" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="10" t="n"/>
       <c r="B72" s="10" t="n"/>
       <c r="C72" s="10" t="n"/>
       <c r="D72" s="10" t="n"/>
+      <c r="E72" s="10" t="n"/>
+      <c r="F72" s="10" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="10" t="n"/>
       <c r="B73" s="10" t="n"/>
       <c r="C73" s="10" t="n"/>
       <c r="D73" s="10" t="n"/>
+      <c r="E73" s="10" t="n"/>
+      <c r="F73" s="10" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="10" t="n"/>
       <c r="B74" s="10" t="n"/>
       <c r="C74" s="10" t="n"/>
       <c r="D74" s="10" t="n"/>
+      <c r="E74" s="10" t="n"/>
+      <c r="F74" s="10" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="10" t="n"/>
       <c r="B75" s="10" t="n"/>
       <c r="C75" s="10" t="n"/>
       <c r="D75" s="10" t="n"/>
+      <c r="E75" s="10" t="n"/>
+      <c r="F75" s="10" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="10" t="n"/>
       <c r="B76" s="10" t="n"/>
       <c r="C76" s="10" t="n"/>
       <c r="D76" s="10" t="n"/>
+      <c r="E76" s="10" t="n"/>
+      <c r="F76" s="10" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="10" t="n"/>
       <c r="B77" s="10" t="n"/>
       <c r="C77" s="10" t="n"/>
       <c r="D77" s="10" t="n"/>
+      <c r="E77" s="10" t="n"/>
+      <c r="F77" s="10" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="10" t="n"/>
       <c r="B78" s="10" t="n"/>
       <c r="C78" s="10" t="n"/>
       <c r="D78" s="10" t="n"/>
+      <c r="E78" s="10" t="n"/>
+      <c r="F78" s="10" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="10" t="n"/>
       <c r="B79" s="10" t="n"/>
       <c r="C79" s="10" t="n"/>
       <c r="D79" s="10" t="n"/>
+      <c r="E79" s="10" t="n"/>
+      <c r="F79" s="10" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="10" t="n"/>
       <c r="B80" s="10" t="n"/>
       <c r="C80" s="10" t="n"/>
       <c r="D80" s="10" t="n"/>
+      <c r="E80" s="10" t="n"/>
+      <c r="F80" s="10" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="10" t="n"/>
       <c r="B81" s="10" t="n"/>
       <c r="C81" s="10" t="n"/>
       <c r="D81" s="10" t="n"/>
+      <c r="E81" s="10" t="n"/>
+      <c r="F81" s="10" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="10" t="n"/>
       <c r="B82" s="10" t="n"/>
       <c r="C82" s="10" t="n"/>
       <c r="D82" s="10" t="n"/>
+      <c r="E82" s="10" t="n"/>
+      <c r="F82" s="10" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="10" t="n"/>
       <c r="B83" s="10" t="n"/>
       <c r="C83" s="10" t="n"/>
       <c r="D83" s="10" t="n"/>
+      <c r="E83" s="10" t="n"/>
+      <c r="F83" s="10" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="10" t="n"/>
       <c r="B84" s="10" t="n"/>
       <c r="C84" s="10" t="n"/>
       <c r="D84" s="10" t="n"/>
+      <c r="E84" s="10" t="n"/>
+      <c r="F84" s="10" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="10" t="n"/>
       <c r="B85" s="10" t="n"/>
       <c r="C85" s="10" t="n"/>
       <c r="D85" s="10" t="n"/>
+      <c r="E85" s="10" t="n"/>
+      <c r="F85" s="10" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="10" t="n"/>
       <c r="B86" s="10" t="n"/>
       <c r="C86" s="10" t="n"/>
       <c r="D86" s="10" t="n"/>
+      <c r="E86" s="10" t="n"/>
+      <c r="F86" s="10" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="10" t="n"/>
       <c r="B87" s="10" t="n"/>
       <c r="C87" s="10" t="n"/>
       <c r="D87" s="10" t="n"/>
+      <c r="E87" s="10" t="n"/>
+      <c r="F87" s="10" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="10" t="n"/>
       <c r="B88" s="10" t="n"/>
       <c r="C88" s="10" t="n"/>
       <c r="D88" s="10" t="n"/>
+      <c r="E88" s="10" t="n"/>
+      <c r="F88" s="10" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="10" t="n"/>
       <c r="B89" s="10" t="n"/>
       <c r="C89" s="10" t="n"/>
       <c r="D89" s="10" t="n"/>
+      <c r="E89" s="10" t="n"/>
+      <c r="F89" s="10" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="10" t="n"/>
       <c r="B90" s="10" t="n"/>
       <c r="C90" s="10" t="n"/>
       <c r="D90" s="10" t="n"/>
+      <c r="E90" s="10" t="n"/>
+      <c r="F90" s="10" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="10" t="n"/>
       <c r="B91" s="10" t="n"/>
       <c r="C91" s="10" t="n"/>
       <c r="D91" s="10" t="n"/>
+      <c r="E91" s="10" t="n"/>
+      <c r="F91" s="10" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="10" t="n"/>
       <c r="B92" s="10" t="n"/>
       <c r="C92" s="10" t="n"/>
       <c r="D92" s="10" t="n"/>
+      <c r="E92" s="10" t="n"/>
+      <c r="F92" s="10" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="10" t="n"/>
       <c r="B93" s="10" t="n"/>
       <c r="C93" s="10" t="n"/>
       <c r="D93" s="10" t="n"/>
+      <c r="E93" s="10" t="n"/>
+      <c r="F93" s="10" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="10" t="n"/>
       <c r="B94" s="10" t="n"/>
       <c r="C94" s="10" t="n"/>
       <c r="D94" s="10" t="n"/>
+      <c r="E94" s="10" t="n"/>
+      <c r="F94" s="10" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="10" t="n"/>
       <c r="B95" s="10" t="n"/>
       <c r="C95" s="10" t="n"/>
       <c r="D95" s="10" t="n"/>
+      <c r="E95" s="10" t="n"/>
+      <c r="F95" s="10" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="10" t="n"/>
       <c r="B96" s="10" t="n"/>
       <c r="C96" s="10" t="n"/>
       <c r="D96" s="10" t="n"/>
+      <c r="E96" s="10" t="n"/>
+      <c r="F96" s="10" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="10" t="n"/>
       <c r="B97" s="10" t="n"/>
       <c r="C97" s="10" t="n"/>
       <c r="D97" s="10" t="n"/>
+      <c r="E97" s="10" t="n"/>
+      <c r="F97" s="10" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="10" t="n"/>
       <c r="B98" s="10" t="n"/>
       <c r="C98" s="10" t="n"/>
       <c r="D98" s="10" t="n"/>
+      <c r="E98" s="10" t="n"/>
+      <c r="F98" s="10" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="10" t="n"/>
       <c r="B99" s="10" t="n"/>
       <c r="C99" s="10" t="n"/>
       <c r="D99" s="10" t="n"/>
+      <c r="E99" s="10" t="n"/>
+      <c r="F99" s="10" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="10" t="n"/>
       <c r="B100" s="10" t="n"/>
       <c r="C100" s="10" t="n"/>
       <c r="D100" s="10" t="n"/>
+      <c r="E100" s="10" t="n"/>
+      <c r="F100" s="10" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="10" t="n"/>
       <c r="B101" s="10" t="n"/>
       <c r="C101" s="10" t="n"/>
       <c r="D101" s="10" t="n"/>
+      <c r="E101" s="10" t="n"/>
+      <c r="F101" s="10" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="10" t="n"/>
       <c r="B102" s="10" t="n"/>
       <c r="C102" s="10" t="n"/>
       <c r="D102" s="10" t="n"/>
+      <c r="E102" s="10" t="n"/>
+      <c r="F102" s="10" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="10" t="n"/>
       <c r="B103" s="10" t="n"/>
       <c r="C103" s="10" t="n"/>
       <c r="D103" s="10" t="n"/>
+      <c r="E103" s="10" t="n"/>
+      <c r="F103" s="10" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="10" t="n"/>
       <c r="B104" s="10" t="n"/>
       <c r="C104" s="10" t="n"/>
       <c r="D104" s="10" t="n"/>
+      <c r="E104" s="10" t="n"/>
+      <c r="F104" s="10" t="n"/>
+    </row>
+    <row r="105"/>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>※ 구분: 자산/부채/자본/수익/비용 · 원가구분: 제조/도급/분양/판관 (같은 계정명이 제조·판관에 모두 있을 때 코드로 구분)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12274,18 +12568,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12316,1439 +12612,1769 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
+          <t>원가구분</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
           <t>계정과목</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>원장 차변합계</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>원장 대변합계</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>조정 차변</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>조정 대변</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>당월 잔액</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>비고</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>매핑행(자동)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="13">
-        <f>IF($B5="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C5,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B5="","",IF(AND($K5&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K5)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K5),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B5&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B5" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C5" s="12">
-        <f>IF($B5="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B5&amp;"#1",원장입력!$L$5:$L$204,0))="",$B5&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B5&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D5" s="15">
+      <c r="C5" s="13">
+        <f>IF($B5="","",IF(AND($K5&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K5)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K5),IF(LEFT($B5,1)="5","제조",IF(LEFT($B5,1)="6","도급",IF(LEFT($B5,1)="7","분양",IF(LEFT($B5,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D5" s="12">
+        <f>IF($B5="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B5&amp;"#1",원장입력!$L$5:$L$204,0))="",$B5&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B5&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C5&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B5&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C5,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E5" s="15">
         <f>IF($B5="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B5))</f>
         <v/>
       </c>
-      <c r="E5" s="15">
+      <c r="F5" s="15">
         <f>IF($B5="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B5))</f>
         <v/>
       </c>
-      <c r="F5" s="15">
-        <f>IF($B5="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B5)+IF($C5=$B5,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C5)))</f>
-        <v/>
-      </c>
       <c r="G5" s="15">
-        <f>IF($B5="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B5)+IF($C5=$B5,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C5)))</f>
+        <f>IF($B5="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B5)+IF($D5=$B5,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D5)))</f>
         <v/>
       </c>
       <c r="H5" s="15">
-        <f>IF($B5="","",IF(OR($A5="자산",$A5="비용"),D5-E5+F5-G5,E5-D5+G5-F5))</f>
-        <v/>
-      </c>
-      <c r="I5" s="16" t="n"/>
+        <f>IF($B5="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B5)+IF($D5=$B5,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D5)))</f>
+        <v/>
+      </c>
+      <c r="I5" s="15">
+        <f>IF($B5="","",IF(OR($A5="자산",$A5="비용"),E5-F5+G5-H5,F5-E5+H5-G5))</f>
+        <v/>
+      </c>
+      <c r="J5" s="16" t="n"/>
+      <c r="K5" s="5">
+        <f>IF($B5="","",IFERROR(MATCH(--$B5,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B5,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="13">
-        <f>IF($B6="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C6,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B6="","",IF(AND($K6&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K6)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K6),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B6&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B6" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C6" s="12">
-        <f>IF($B6="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B6&amp;"#1",원장입력!$L$5:$L$204,0))="",$B6&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B6&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D6" s="15">
+      <c r="C6" s="13">
+        <f>IF($B6="","",IF(AND($K6&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K6)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K6),IF(LEFT($B6,1)="5","제조",IF(LEFT($B6,1)="6","도급",IF(LEFT($B6,1)="7","분양",IF(LEFT($B6,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D6" s="12">
+        <f>IF($B6="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B6&amp;"#1",원장입력!$L$5:$L$204,0))="",$B6&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B6&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C6&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B6&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C6,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E6" s="15">
         <f>IF($B6="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B6))</f>
         <v/>
       </c>
-      <c r="E6" s="15">
+      <c r="F6" s="15">
         <f>IF($B6="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B6))</f>
         <v/>
       </c>
-      <c r="F6" s="15">
-        <f>IF($B6="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B6)+IF($C6=$B6,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C6)))</f>
-        <v/>
-      </c>
       <c r="G6" s="15">
-        <f>IF($B6="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B6)+IF($C6=$B6,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C6)))</f>
+        <f>IF($B6="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B6)+IF($D6=$B6,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D6)))</f>
         <v/>
       </c>
       <c r="H6" s="15">
-        <f>IF($B6="","",IF(OR($A6="자산",$A6="비용"),D6-E6+F6-G6,E6-D6+G6-F6))</f>
-        <v/>
-      </c>
-      <c r="I6" s="16" t="n"/>
+        <f>IF($B6="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B6)+IF($D6=$B6,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D6)))</f>
+        <v/>
+      </c>
+      <c r="I6" s="15">
+        <f>IF($B6="","",IF(OR($A6="자산",$A6="비용"),E6-F6+G6-H6,F6-E6+H6-G6))</f>
+        <v/>
+      </c>
+      <c r="J6" s="16" t="n"/>
+      <c r="K6" s="5">
+        <f>IF($B6="","",IFERROR(MATCH(--$B6,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B6,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="13">
-        <f>IF($B7="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C7,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B7="","",IF(AND($K7&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K7)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K7),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B7&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B7" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C7" s="12">
-        <f>IF($B7="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B7&amp;"#1",원장입력!$L$5:$L$204,0))="",$B7&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B7&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D7" s="15">
+      <c r="C7" s="13">
+        <f>IF($B7="","",IF(AND($K7&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K7)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K7),IF(LEFT($B7,1)="5","제조",IF(LEFT($B7,1)="6","도급",IF(LEFT($B7,1)="7","분양",IF(LEFT($B7,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D7" s="12">
+        <f>IF($B7="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B7&amp;"#1",원장입력!$L$5:$L$204,0))="",$B7&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B7&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C7&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B7&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C7,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E7" s="15">
         <f>IF($B7="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B7))</f>
         <v/>
       </c>
-      <c r="E7" s="15">
+      <c r="F7" s="15">
         <f>IF($B7="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B7))</f>
         <v/>
       </c>
-      <c r="F7" s="15">
-        <f>IF($B7="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B7)+IF($C7=$B7,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C7)))</f>
-        <v/>
-      </c>
       <c r="G7" s="15">
-        <f>IF($B7="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B7)+IF($C7=$B7,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C7)))</f>
+        <f>IF($B7="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B7)+IF($D7=$B7,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D7)))</f>
         <v/>
       </c>
       <c r="H7" s="15">
-        <f>IF($B7="","",IF(OR($A7="자산",$A7="비용"),D7-E7+F7-G7,E7-D7+G7-F7))</f>
-        <v/>
-      </c>
-      <c r="I7" s="16" t="n"/>
+        <f>IF($B7="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B7)+IF($D7=$B7,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D7)))</f>
+        <v/>
+      </c>
+      <c r="I7" s="15">
+        <f>IF($B7="","",IF(OR($A7="자산",$A7="비용"),E7-F7+G7-H7,F7-E7+H7-G7))</f>
+        <v/>
+      </c>
+      <c r="J7" s="16" t="n"/>
+      <c r="K7" s="5">
+        <f>IF($B7="","",IFERROR(MATCH(--$B7,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B7,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="13">
-        <f>IF($B8="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C8,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B8="","",IF(AND($K8&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K8)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K8),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B8&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B8" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C8" s="12">
-        <f>IF($B8="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B8&amp;"#1",원장입력!$L$5:$L$204,0))="",$B8&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B8&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D8" s="15">
+      <c r="C8" s="13">
+        <f>IF($B8="","",IF(AND($K8&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K8)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K8),IF(LEFT($B8,1)="5","제조",IF(LEFT($B8,1)="6","도급",IF(LEFT($B8,1)="7","분양",IF(LEFT($B8,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D8" s="12">
+        <f>IF($B8="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B8&amp;"#1",원장입력!$L$5:$L$204,0))="",$B8&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B8&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C8&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B8&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C8,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E8" s="15">
         <f>IF($B8="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B8))</f>
         <v/>
       </c>
-      <c r="E8" s="15">
+      <c r="F8" s="15">
         <f>IF($B8="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B8))</f>
         <v/>
       </c>
-      <c r="F8" s="15">
-        <f>IF($B8="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B8)+IF($C8=$B8,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C8)))</f>
-        <v/>
-      </c>
       <c r="G8" s="15">
-        <f>IF($B8="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B8)+IF($C8=$B8,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C8)))</f>
+        <f>IF($B8="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B8)+IF($D8=$B8,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D8)))</f>
         <v/>
       </c>
       <c r="H8" s="15">
-        <f>IF($B8="","",IF(OR($A8="자산",$A8="비용"),D8-E8+F8-G8,E8-D8+G8-F8))</f>
-        <v/>
-      </c>
-      <c r="I8" s="16" t="n"/>
+        <f>IF($B8="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B8)+IF($D8=$B8,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D8)))</f>
+        <v/>
+      </c>
+      <c r="I8" s="15">
+        <f>IF($B8="","",IF(OR($A8="자산",$A8="비용"),E8-F8+G8-H8,F8-E8+H8-G8))</f>
+        <v/>
+      </c>
+      <c r="J8" s="16" t="n"/>
+      <c r="K8" s="5">
+        <f>IF($B8="","",IFERROR(MATCH(--$B8,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B8,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="13">
-        <f>IF($B9="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C9,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B9="","",IF(AND($K9&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K9)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K9),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B9&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B9" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C9" s="12">
-        <f>IF($B9="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B9&amp;"#1",원장입력!$L$5:$L$204,0))="",$B9&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B9&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D9" s="15">
+      <c r="C9" s="13">
+        <f>IF($B9="","",IF(AND($K9&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K9)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K9),IF(LEFT($B9,1)="5","제조",IF(LEFT($B9,1)="6","도급",IF(LEFT($B9,1)="7","분양",IF(LEFT($B9,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D9" s="12">
+        <f>IF($B9="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B9&amp;"#1",원장입력!$L$5:$L$204,0))="",$B9&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B9&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C9&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B9&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C9,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E9" s="15">
         <f>IF($B9="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B9))</f>
         <v/>
       </c>
-      <c r="E9" s="15">
+      <c r="F9" s="15">
         <f>IF($B9="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B9))</f>
         <v/>
       </c>
-      <c r="F9" s="15">
-        <f>IF($B9="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B9)+IF($C9=$B9,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C9)))</f>
-        <v/>
-      </c>
       <c r="G9" s="15">
-        <f>IF($B9="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B9)+IF($C9=$B9,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C9)))</f>
+        <f>IF($B9="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B9)+IF($D9=$B9,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D9)))</f>
         <v/>
       </c>
       <c r="H9" s="15">
-        <f>IF($B9="","",IF(OR($A9="자산",$A9="비용"),D9-E9+F9-G9,E9-D9+G9-F9))</f>
-        <v/>
-      </c>
-      <c r="I9" s="16" t="n"/>
+        <f>IF($B9="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B9)+IF($D9=$B9,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D9)))</f>
+        <v/>
+      </c>
+      <c r="I9" s="15">
+        <f>IF($B9="","",IF(OR($A9="자산",$A9="비용"),E9-F9+G9-H9,F9-E9+H9-G9))</f>
+        <v/>
+      </c>
+      <c r="J9" s="16" t="n"/>
+      <c r="K9" s="5">
+        <f>IF($B9="","",IFERROR(MATCH(--$B9,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B9,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="13">
-        <f>IF($B10="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C10,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B10="","",IF(AND($K10&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K10)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K10),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B10&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B10" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C10" s="12">
-        <f>IF($B10="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B10&amp;"#1",원장입력!$L$5:$L$204,0))="",$B10&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B10&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D10" s="15">
+      <c r="C10" s="13">
+        <f>IF($B10="","",IF(AND($K10&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K10)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K10),IF(LEFT($B10,1)="5","제조",IF(LEFT($B10,1)="6","도급",IF(LEFT($B10,1)="7","분양",IF(LEFT($B10,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D10" s="12">
+        <f>IF($B10="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B10&amp;"#1",원장입력!$L$5:$L$204,0))="",$B10&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B10&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C10&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B10&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C10,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E10" s="15">
         <f>IF($B10="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B10))</f>
         <v/>
       </c>
-      <c r="E10" s="15">
+      <c r="F10" s="15">
         <f>IF($B10="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B10))</f>
         <v/>
       </c>
-      <c r="F10" s="15">
-        <f>IF($B10="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B10)+IF($C10=$B10,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C10)))</f>
-        <v/>
-      </c>
       <c r="G10" s="15">
-        <f>IF($B10="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B10)+IF($C10=$B10,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C10)))</f>
+        <f>IF($B10="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B10)+IF($D10=$B10,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D10)))</f>
         <v/>
       </c>
       <c r="H10" s="15">
-        <f>IF($B10="","",IF(OR($A10="자산",$A10="비용"),D10-E10+F10-G10,E10-D10+G10-F10))</f>
-        <v/>
-      </c>
-      <c r="I10" s="16" t="n"/>
+        <f>IF($B10="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B10)+IF($D10=$B10,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D10)))</f>
+        <v/>
+      </c>
+      <c r="I10" s="15">
+        <f>IF($B10="","",IF(OR($A10="자산",$A10="비용"),E10-F10+G10-H10,F10-E10+H10-G10))</f>
+        <v/>
+      </c>
+      <c r="J10" s="16" t="n"/>
+      <c r="K10" s="5">
+        <f>IF($B10="","",IFERROR(MATCH(--$B10,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B10,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="13">
-        <f>IF($B11="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C11,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B11="","",IF(AND($K11&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K11)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K11),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B11&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B11" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C11" s="12">
-        <f>IF($B11="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B11&amp;"#1",원장입력!$L$5:$L$204,0))="",$B11&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B11&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D11" s="15">
+      <c r="C11" s="13">
+        <f>IF($B11="","",IF(AND($K11&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K11)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K11),IF(LEFT($B11,1)="5","제조",IF(LEFT($B11,1)="6","도급",IF(LEFT($B11,1)="7","분양",IF(LEFT($B11,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D11" s="12">
+        <f>IF($B11="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B11&amp;"#1",원장입력!$L$5:$L$204,0))="",$B11&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B11&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C11&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B11&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C11,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E11" s="15">
         <f>IF($B11="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B11))</f>
         <v/>
       </c>
-      <c r="E11" s="15">
+      <c r="F11" s="15">
         <f>IF($B11="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B11))</f>
         <v/>
       </c>
-      <c r="F11" s="15">
-        <f>IF($B11="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B11)+IF($C11=$B11,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C11)))</f>
-        <v/>
-      </c>
       <c r="G11" s="15">
-        <f>IF($B11="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B11)+IF($C11=$B11,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C11)))</f>
+        <f>IF($B11="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B11)+IF($D11=$B11,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D11)))</f>
         <v/>
       </c>
       <c r="H11" s="15">
-        <f>IF($B11="","",IF(OR($A11="자산",$A11="비용"),D11-E11+F11-G11,E11-D11+G11-F11))</f>
-        <v/>
-      </c>
-      <c r="I11" s="16" t="n"/>
+        <f>IF($B11="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B11)+IF($D11=$B11,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D11)))</f>
+        <v/>
+      </c>
+      <c r="I11" s="15">
+        <f>IF($B11="","",IF(OR($A11="자산",$A11="비용"),E11-F11+G11-H11,F11-E11+H11-G11))</f>
+        <v/>
+      </c>
+      <c r="J11" s="16" t="n"/>
+      <c r="K11" s="5">
+        <f>IF($B11="","",IFERROR(MATCH(--$B11,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B11,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="13">
-        <f>IF($B12="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C12,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B12="","",IF(AND($K12&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K12)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K12),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B12&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B12" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C12" s="12">
-        <f>IF($B12="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B12&amp;"#1",원장입력!$L$5:$L$204,0))="",$B12&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B12&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D12" s="15">
+      <c r="C12" s="13">
+        <f>IF($B12="","",IF(AND($K12&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K12)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K12),IF(LEFT($B12,1)="5","제조",IF(LEFT($B12,1)="6","도급",IF(LEFT($B12,1)="7","분양",IF(LEFT($B12,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D12" s="12">
+        <f>IF($B12="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B12&amp;"#1",원장입력!$L$5:$L$204,0))="",$B12&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B12&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C12&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B12&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C12,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E12" s="15">
         <f>IF($B12="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B12))</f>
         <v/>
       </c>
-      <c r="E12" s="15">
+      <c r="F12" s="15">
         <f>IF($B12="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B12))</f>
         <v/>
       </c>
-      <c r="F12" s="15">
-        <f>IF($B12="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B12)+IF($C12=$B12,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C12)))</f>
-        <v/>
-      </c>
       <c r="G12" s="15">
-        <f>IF($B12="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B12)+IF($C12=$B12,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C12)))</f>
+        <f>IF($B12="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B12)+IF($D12=$B12,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D12)))</f>
         <v/>
       </c>
       <c r="H12" s="15">
-        <f>IF($B12="","",IF(OR($A12="자산",$A12="비용"),D12-E12+F12-G12,E12-D12+G12-F12))</f>
-        <v/>
-      </c>
-      <c r="I12" s="16" t="n"/>
+        <f>IF($B12="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B12)+IF($D12=$B12,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D12)))</f>
+        <v/>
+      </c>
+      <c r="I12" s="15">
+        <f>IF($B12="","",IF(OR($A12="자산",$A12="비용"),E12-F12+G12-H12,F12-E12+H12-G12))</f>
+        <v/>
+      </c>
+      <c r="J12" s="16" t="n"/>
+      <c r="K12" s="5">
+        <f>IF($B12="","",IFERROR(MATCH(--$B12,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B12,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="13">
-        <f>IF($B13="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C13,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B13="","",IF(AND($K13&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K13)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K13),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B13&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B13" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C13" s="12">
-        <f>IF($B13="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B13&amp;"#1",원장입력!$L$5:$L$204,0))="",$B13&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B13&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D13" s="15">
+      <c r="C13" s="13">
+        <f>IF($B13="","",IF(AND($K13&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K13)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K13),IF(LEFT($B13,1)="5","제조",IF(LEFT($B13,1)="6","도급",IF(LEFT($B13,1)="7","분양",IF(LEFT($B13,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D13" s="12">
+        <f>IF($B13="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B13&amp;"#1",원장입력!$L$5:$L$204,0))="",$B13&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B13&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C13&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B13&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C13,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E13" s="15">
         <f>IF($B13="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B13))</f>
         <v/>
       </c>
-      <c r="E13" s="15">
+      <c r="F13" s="15">
         <f>IF($B13="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B13))</f>
         <v/>
       </c>
-      <c r="F13" s="15">
-        <f>IF($B13="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B13)+IF($C13=$B13,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C13)))</f>
-        <v/>
-      </c>
       <c r="G13" s="15">
-        <f>IF($B13="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B13)+IF($C13=$B13,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C13)))</f>
+        <f>IF($B13="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B13)+IF($D13=$B13,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D13)))</f>
         <v/>
       </c>
       <c r="H13" s="15">
-        <f>IF($B13="","",IF(OR($A13="자산",$A13="비용"),D13-E13+F13-G13,E13-D13+G13-F13))</f>
-        <v/>
-      </c>
-      <c r="I13" s="16" t="n"/>
+        <f>IF($B13="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B13)+IF($D13=$B13,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D13)))</f>
+        <v/>
+      </c>
+      <c r="I13" s="15">
+        <f>IF($B13="","",IF(OR($A13="자산",$A13="비용"),E13-F13+G13-H13,F13-E13+H13-G13))</f>
+        <v/>
+      </c>
+      <c r="J13" s="16" t="n"/>
+      <c r="K13" s="5">
+        <f>IF($B13="","",IFERROR(MATCH(--$B13,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B13,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="13">
-        <f>IF($B14="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C14,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B14="","",IF(AND($K14&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K14)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K14),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B14&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B14" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C14" s="12">
-        <f>IF($B14="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B14&amp;"#1",원장입력!$L$5:$L$204,0))="",$B14&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B14&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D14" s="15">
+      <c r="C14" s="13">
+        <f>IF($B14="","",IF(AND($K14&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K14)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K14),IF(LEFT($B14,1)="5","제조",IF(LEFT($B14,1)="6","도급",IF(LEFT($B14,1)="7","분양",IF(LEFT($B14,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D14" s="12">
+        <f>IF($B14="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B14&amp;"#1",원장입력!$L$5:$L$204,0))="",$B14&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B14&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C14&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B14&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C14,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E14" s="15">
         <f>IF($B14="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B14))</f>
         <v/>
       </c>
-      <c r="E14" s="15">
+      <c r="F14" s="15">
         <f>IF($B14="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B14))</f>
         <v/>
       </c>
-      <c r="F14" s="15">
-        <f>IF($B14="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B14)+IF($C14=$B14,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C14)))</f>
-        <v/>
-      </c>
       <c r="G14" s="15">
-        <f>IF($B14="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B14)+IF($C14=$B14,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C14)))</f>
+        <f>IF($B14="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B14)+IF($D14=$B14,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D14)))</f>
         <v/>
       </c>
       <c r="H14" s="15">
-        <f>IF($B14="","",IF(OR($A14="자산",$A14="비용"),D14-E14+F14-G14,E14-D14+G14-F14))</f>
-        <v/>
-      </c>
-      <c r="I14" s="16" t="n"/>
+        <f>IF($B14="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B14)+IF($D14=$B14,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D14)))</f>
+        <v/>
+      </c>
+      <c r="I14" s="15">
+        <f>IF($B14="","",IF(OR($A14="자산",$A14="비용"),E14-F14+G14-H14,F14-E14+H14-G14))</f>
+        <v/>
+      </c>
+      <c r="J14" s="16" t="n"/>
+      <c r="K14" s="5">
+        <f>IF($B14="","",IFERROR(MATCH(--$B14,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B14,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="13">
-        <f>IF($B15="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C15,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B15="","",IF(AND($K15&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K15)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K15),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B15&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B15" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C15" s="12">
-        <f>IF($B15="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B15&amp;"#1",원장입력!$L$5:$L$204,0))="",$B15&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B15&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D15" s="15">
+      <c r="C15" s="13">
+        <f>IF($B15="","",IF(AND($K15&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K15)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K15),IF(LEFT($B15,1)="5","제조",IF(LEFT($B15,1)="6","도급",IF(LEFT($B15,1)="7","분양",IF(LEFT($B15,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D15" s="12">
+        <f>IF($B15="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B15&amp;"#1",원장입력!$L$5:$L$204,0))="",$B15&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B15&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C15&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B15&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C15,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E15" s="15">
         <f>IF($B15="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B15))</f>
         <v/>
       </c>
-      <c r="E15" s="15">
+      <c r="F15" s="15">
         <f>IF($B15="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B15))</f>
         <v/>
       </c>
-      <c r="F15" s="15">
-        <f>IF($B15="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B15)+IF($C15=$B15,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C15)))</f>
-        <v/>
-      </c>
       <c r="G15" s="15">
-        <f>IF($B15="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B15)+IF($C15=$B15,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C15)))</f>
+        <f>IF($B15="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B15)+IF($D15=$B15,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D15)))</f>
         <v/>
       </c>
       <c r="H15" s="15">
-        <f>IF($B15="","",IF(OR($A15="자산",$A15="비용"),D15-E15+F15-G15,E15-D15+G15-F15))</f>
-        <v/>
-      </c>
-      <c r="I15" s="16" t="n"/>
+        <f>IF($B15="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B15)+IF($D15=$B15,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D15)))</f>
+        <v/>
+      </c>
+      <c r="I15" s="15">
+        <f>IF($B15="","",IF(OR($A15="자산",$A15="비용"),E15-F15+G15-H15,F15-E15+H15-G15))</f>
+        <v/>
+      </c>
+      <c r="J15" s="16" t="n"/>
+      <c r="K15" s="5">
+        <f>IF($B15="","",IFERROR(MATCH(--$B15,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B15,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="13">
-        <f>IF($B16="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C16,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B16="","",IF(AND($K16&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K16)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K16),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B16&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B16" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C16" s="12">
-        <f>IF($B16="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B16&amp;"#1",원장입력!$L$5:$L$204,0))="",$B16&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B16&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D16" s="15">
+      <c r="C16" s="13">
+        <f>IF($B16="","",IF(AND($K16&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K16)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K16),IF(LEFT($B16,1)="5","제조",IF(LEFT($B16,1)="6","도급",IF(LEFT($B16,1)="7","분양",IF(LEFT($B16,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D16" s="12">
+        <f>IF($B16="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B16&amp;"#1",원장입력!$L$5:$L$204,0))="",$B16&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B16&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C16&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B16&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C16,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E16" s="15">
         <f>IF($B16="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B16))</f>
         <v/>
       </c>
-      <c r="E16" s="15">
+      <c r="F16" s="15">
         <f>IF($B16="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B16))</f>
         <v/>
       </c>
-      <c r="F16" s="15">
-        <f>IF($B16="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B16)+IF($C16=$B16,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C16)))</f>
-        <v/>
-      </c>
       <c r="G16" s="15">
-        <f>IF($B16="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B16)+IF($C16=$B16,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C16)))</f>
+        <f>IF($B16="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B16)+IF($D16=$B16,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D16)))</f>
         <v/>
       </c>
       <c r="H16" s="15">
-        <f>IF($B16="","",IF(OR($A16="자산",$A16="비용"),D16-E16+F16-G16,E16-D16+G16-F16))</f>
-        <v/>
-      </c>
-      <c r="I16" s="16" t="n"/>
+        <f>IF($B16="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B16)+IF($D16=$B16,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D16)))</f>
+        <v/>
+      </c>
+      <c r="I16" s="15">
+        <f>IF($B16="","",IF(OR($A16="자산",$A16="비용"),E16-F16+G16-H16,F16-E16+H16-G16))</f>
+        <v/>
+      </c>
+      <c r="J16" s="16" t="n"/>
+      <c r="K16" s="5">
+        <f>IF($B16="","",IFERROR(MATCH(--$B16,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B16,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>IF($B17="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C17,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B17="","",IF(AND($K17&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K17)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K17),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B17&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B17" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C17" s="12">
-        <f>IF($B17="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B17&amp;"#1",원장입력!$L$5:$L$204,0))="",$B17&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B17&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D17" s="15">
+      <c r="C17" s="13">
+        <f>IF($B17="","",IF(AND($K17&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K17)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K17),IF(LEFT($B17,1)="5","제조",IF(LEFT($B17,1)="6","도급",IF(LEFT($B17,1)="7","분양",IF(LEFT($B17,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D17" s="12">
+        <f>IF($B17="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B17&amp;"#1",원장입력!$L$5:$L$204,0))="",$B17&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B17&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C17&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B17&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C17,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E17" s="15">
         <f>IF($B17="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B17))</f>
         <v/>
       </c>
-      <c r="E17" s="15">
+      <c r="F17" s="15">
         <f>IF($B17="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B17))</f>
         <v/>
       </c>
-      <c r="F17" s="15">
-        <f>IF($B17="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B17)+IF($C17=$B17,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C17)))</f>
-        <v/>
-      </c>
       <c r="G17" s="15">
-        <f>IF($B17="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B17)+IF($C17=$B17,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C17)))</f>
+        <f>IF($B17="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B17)+IF($D17=$B17,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D17)))</f>
         <v/>
       </c>
       <c r="H17" s="15">
-        <f>IF($B17="","",IF(OR($A17="자산",$A17="비용"),D17-E17+F17-G17,E17-D17+G17-F17))</f>
-        <v/>
-      </c>
-      <c r="I17" s="16" t="n"/>
+        <f>IF($B17="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B17)+IF($D17=$B17,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D17)))</f>
+        <v/>
+      </c>
+      <c r="I17" s="15">
+        <f>IF($B17="","",IF(OR($A17="자산",$A17="비용"),E17-F17+G17-H17,F17-E17+H17-G17))</f>
+        <v/>
+      </c>
+      <c r="J17" s="16" t="n"/>
+      <c r="K17" s="5">
+        <f>IF($B17="","",IFERROR(MATCH(--$B17,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B17,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="13">
-        <f>IF($B18="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C18,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B18="","",IF(AND($K18&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K18)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K18),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B18&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B18" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C18" s="12">
-        <f>IF($B18="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B18&amp;"#1",원장입력!$L$5:$L$204,0))="",$B18&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B18&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D18" s="15">
+      <c r="C18" s="13">
+        <f>IF($B18="","",IF(AND($K18&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K18)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K18),IF(LEFT($B18,1)="5","제조",IF(LEFT($B18,1)="6","도급",IF(LEFT($B18,1)="7","분양",IF(LEFT($B18,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D18" s="12">
+        <f>IF($B18="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B18&amp;"#1",원장입력!$L$5:$L$204,0))="",$B18&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B18&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C18&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B18&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C18,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E18" s="15">
         <f>IF($B18="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B18))</f>
         <v/>
       </c>
-      <c r="E18" s="15">
+      <c r="F18" s="15">
         <f>IF($B18="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B18))</f>
         <v/>
       </c>
-      <c r="F18" s="15">
-        <f>IF($B18="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B18)+IF($C18=$B18,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C18)))</f>
-        <v/>
-      </c>
       <c r="G18" s="15">
-        <f>IF($B18="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B18)+IF($C18=$B18,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C18)))</f>
+        <f>IF($B18="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B18)+IF($D18=$B18,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D18)))</f>
         <v/>
       </c>
       <c r="H18" s="15">
-        <f>IF($B18="","",IF(OR($A18="자산",$A18="비용"),D18-E18+F18-G18,E18-D18+G18-F18))</f>
-        <v/>
-      </c>
-      <c r="I18" s="16" t="n"/>
+        <f>IF($B18="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B18)+IF($D18=$B18,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D18)))</f>
+        <v/>
+      </c>
+      <c r="I18" s="15">
+        <f>IF($B18="","",IF(OR($A18="자산",$A18="비용"),E18-F18+G18-H18,F18-E18+H18-G18))</f>
+        <v/>
+      </c>
+      <c r="J18" s="16" t="n"/>
+      <c r="K18" s="5">
+        <f>IF($B18="","",IFERROR(MATCH(--$B18,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B18,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="13">
-        <f>IF($B19="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C19,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B19="","",IF(AND($K19&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K19)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K19),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B19&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B19" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C19" s="12">
-        <f>IF($B19="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B19&amp;"#1",원장입력!$L$5:$L$204,0))="",$B19&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B19&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D19" s="15">
+      <c r="C19" s="13">
+        <f>IF($B19="","",IF(AND($K19&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K19)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K19),IF(LEFT($B19,1)="5","제조",IF(LEFT($B19,1)="6","도급",IF(LEFT($B19,1)="7","분양",IF(LEFT($B19,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D19" s="12">
+        <f>IF($B19="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B19&amp;"#1",원장입력!$L$5:$L$204,0))="",$B19&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B19&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C19&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B19&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C19,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E19" s="15">
         <f>IF($B19="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B19))</f>
         <v/>
       </c>
-      <c r="E19" s="15">
+      <c r="F19" s="15">
         <f>IF($B19="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B19))</f>
         <v/>
       </c>
-      <c r="F19" s="15">
-        <f>IF($B19="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B19)+IF($C19=$B19,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C19)))</f>
-        <v/>
-      </c>
       <c r="G19" s="15">
-        <f>IF($B19="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B19)+IF($C19=$B19,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C19)))</f>
+        <f>IF($B19="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B19)+IF($D19=$B19,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D19)))</f>
         <v/>
       </c>
       <c r="H19" s="15">
-        <f>IF($B19="","",IF(OR($A19="자산",$A19="비용"),D19-E19+F19-G19,E19-D19+G19-F19))</f>
-        <v/>
-      </c>
-      <c r="I19" s="16" t="n"/>
+        <f>IF($B19="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B19)+IF($D19=$B19,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D19)))</f>
+        <v/>
+      </c>
+      <c r="I19" s="15">
+        <f>IF($B19="","",IF(OR($A19="자산",$A19="비용"),E19-F19+G19-H19,F19-E19+H19-G19))</f>
+        <v/>
+      </c>
+      <c r="J19" s="16" t="n"/>
+      <c r="K19" s="5">
+        <f>IF($B19="","",IFERROR(MATCH(--$B19,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B19,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>IF($B20="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C20,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B20="","",IF(AND($K20&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K20)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K20),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B20&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B20" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C20" s="12">
-        <f>IF($B20="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B20&amp;"#1",원장입력!$L$5:$L$204,0))="",$B20&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B20&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D20" s="15">
+      <c r="C20" s="13">
+        <f>IF($B20="","",IF(AND($K20&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K20)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K20),IF(LEFT($B20,1)="5","제조",IF(LEFT($B20,1)="6","도급",IF(LEFT($B20,1)="7","분양",IF(LEFT($B20,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D20" s="12">
+        <f>IF($B20="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B20&amp;"#1",원장입력!$L$5:$L$204,0))="",$B20&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B20&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C20&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B20&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C20,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E20" s="15">
         <f>IF($B20="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B20))</f>
         <v/>
       </c>
-      <c r="E20" s="15">
+      <c r="F20" s="15">
         <f>IF($B20="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B20))</f>
         <v/>
       </c>
-      <c r="F20" s="15">
-        <f>IF($B20="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B20)+IF($C20=$B20,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C20)))</f>
-        <v/>
-      </c>
       <c r="G20" s="15">
-        <f>IF($B20="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B20)+IF($C20=$B20,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C20)))</f>
+        <f>IF($B20="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B20)+IF($D20=$B20,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D20)))</f>
         <v/>
       </c>
       <c r="H20" s="15">
-        <f>IF($B20="","",IF(OR($A20="자산",$A20="비용"),D20-E20+F20-G20,E20-D20+G20-F20))</f>
-        <v/>
-      </c>
-      <c r="I20" s="16" t="n"/>
+        <f>IF($B20="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B20)+IF($D20=$B20,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D20)))</f>
+        <v/>
+      </c>
+      <c r="I20" s="15">
+        <f>IF($B20="","",IF(OR($A20="자산",$A20="비용"),E20-F20+G20-H20,F20-E20+H20-G20))</f>
+        <v/>
+      </c>
+      <c r="J20" s="16" t="n"/>
+      <c r="K20" s="5">
+        <f>IF($B20="","",IFERROR(MATCH(--$B20,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B20,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="13">
-        <f>IF($B21="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C21,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B21="","",IF(AND($K21&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K21)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K21),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B21&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B21" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C21" s="12">
-        <f>IF($B21="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B21&amp;"#1",원장입력!$L$5:$L$204,0))="",$B21&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B21&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D21" s="15">
+      <c r="C21" s="13">
+        <f>IF($B21="","",IF(AND($K21&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K21)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K21),IF(LEFT($B21,1)="5","제조",IF(LEFT($B21,1)="6","도급",IF(LEFT($B21,1)="7","분양",IF(LEFT($B21,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D21" s="12">
+        <f>IF($B21="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B21&amp;"#1",원장입력!$L$5:$L$204,0))="",$B21&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B21&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C21&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B21&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C21,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E21" s="15">
         <f>IF($B21="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B21))</f>
         <v/>
       </c>
-      <c r="E21" s="15">
+      <c r="F21" s="15">
         <f>IF($B21="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B21))</f>
         <v/>
       </c>
-      <c r="F21" s="15">
-        <f>IF($B21="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B21)+IF($C21=$B21,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C21)))</f>
-        <v/>
-      </c>
       <c r="G21" s="15">
-        <f>IF($B21="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B21)+IF($C21=$B21,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C21)))</f>
+        <f>IF($B21="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B21)+IF($D21=$B21,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D21)))</f>
         <v/>
       </c>
       <c r="H21" s="15">
-        <f>IF($B21="","",IF(OR($A21="자산",$A21="비용"),D21-E21+F21-G21,E21-D21+G21-F21))</f>
-        <v/>
-      </c>
-      <c r="I21" s="16" t="n"/>
+        <f>IF($B21="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B21)+IF($D21=$B21,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D21)))</f>
+        <v/>
+      </c>
+      <c r="I21" s="15">
+        <f>IF($B21="","",IF(OR($A21="자산",$A21="비용"),E21-F21+G21-H21,F21-E21+H21-G21))</f>
+        <v/>
+      </c>
+      <c r="J21" s="16" t="n"/>
+      <c r="K21" s="5">
+        <f>IF($B21="","",IFERROR(MATCH(--$B21,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B21,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="13">
-        <f>IF($B22="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C22,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B22="","",IF(AND($K22&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K22)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K22),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B22&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B22" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C22" s="12">
-        <f>IF($B22="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B22&amp;"#1",원장입력!$L$5:$L$204,0))="",$B22&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B22&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D22" s="15">
+      <c r="C22" s="13">
+        <f>IF($B22="","",IF(AND($K22&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K22)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K22),IF(LEFT($B22,1)="5","제조",IF(LEFT($B22,1)="6","도급",IF(LEFT($B22,1)="7","분양",IF(LEFT($B22,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D22" s="12">
+        <f>IF($B22="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B22&amp;"#1",원장입력!$L$5:$L$204,0))="",$B22&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B22&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C22&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B22&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C22,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E22" s="15">
         <f>IF($B22="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B22))</f>
         <v/>
       </c>
-      <c r="E22" s="15">
+      <c r="F22" s="15">
         <f>IF($B22="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B22))</f>
         <v/>
       </c>
-      <c r="F22" s="15">
-        <f>IF($B22="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B22)+IF($C22=$B22,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C22)))</f>
-        <v/>
-      </c>
       <c r="G22" s="15">
-        <f>IF($B22="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B22)+IF($C22=$B22,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C22)))</f>
+        <f>IF($B22="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B22)+IF($D22=$B22,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D22)))</f>
         <v/>
       </c>
       <c r="H22" s="15">
-        <f>IF($B22="","",IF(OR($A22="자산",$A22="비용"),D22-E22+F22-G22,E22-D22+G22-F22))</f>
-        <v/>
-      </c>
-      <c r="I22" s="16" t="n"/>
+        <f>IF($B22="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B22)+IF($D22=$B22,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D22)))</f>
+        <v/>
+      </c>
+      <c r="I22" s="15">
+        <f>IF($B22="","",IF(OR($A22="자산",$A22="비용"),E22-F22+G22-H22,F22-E22+H22-G22))</f>
+        <v/>
+      </c>
+      <c r="J22" s="16" t="n"/>
+      <c r="K22" s="5">
+        <f>IF($B22="","",IFERROR(MATCH(--$B22,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B22,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="13">
-        <f>IF($B23="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C23,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B23="","",IF(AND($K23&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K23)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K23),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B23&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B23" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C23" s="12">
-        <f>IF($B23="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B23&amp;"#1",원장입력!$L$5:$L$204,0))="",$B23&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B23&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D23" s="15">
+      <c r="C23" s="13">
+        <f>IF($B23="","",IF(AND($K23&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K23)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K23),IF(LEFT($B23,1)="5","제조",IF(LEFT($B23,1)="6","도급",IF(LEFT($B23,1)="7","분양",IF(LEFT($B23,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D23" s="12">
+        <f>IF($B23="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B23&amp;"#1",원장입력!$L$5:$L$204,0))="",$B23&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B23&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C23&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B23&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C23,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E23" s="15">
         <f>IF($B23="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B23))</f>
         <v/>
       </c>
-      <c r="E23" s="15">
+      <c r="F23" s="15">
         <f>IF($B23="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B23))</f>
         <v/>
       </c>
-      <c r="F23" s="15">
-        <f>IF($B23="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B23)+IF($C23=$B23,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C23)))</f>
-        <v/>
-      </c>
       <c r="G23" s="15">
-        <f>IF($B23="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B23)+IF($C23=$B23,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C23)))</f>
+        <f>IF($B23="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B23)+IF($D23=$B23,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D23)))</f>
         <v/>
       </c>
       <c r="H23" s="15">
-        <f>IF($B23="","",IF(OR($A23="자산",$A23="비용"),D23-E23+F23-G23,E23-D23+G23-F23))</f>
-        <v/>
-      </c>
-      <c r="I23" s="16" t="n"/>
+        <f>IF($B23="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B23)+IF($D23=$B23,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D23)))</f>
+        <v/>
+      </c>
+      <c r="I23" s="15">
+        <f>IF($B23="","",IF(OR($A23="자산",$A23="비용"),E23-F23+G23-H23,F23-E23+H23-G23))</f>
+        <v/>
+      </c>
+      <c r="J23" s="16" t="n"/>
+      <c r="K23" s="5">
+        <f>IF($B23="","",IFERROR(MATCH(--$B23,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B23,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="13">
-        <f>IF($B24="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C24,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B24="","",IF(AND($K24&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K24)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K24),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B24&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B24" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C24" s="12">
-        <f>IF($B24="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B24&amp;"#1",원장입력!$L$5:$L$204,0))="",$B24&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B24&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D24" s="15">
+      <c r="C24" s="13">
+        <f>IF($B24="","",IF(AND($K24&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K24)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K24),IF(LEFT($B24,1)="5","제조",IF(LEFT($B24,1)="6","도급",IF(LEFT($B24,1)="7","분양",IF(LEFT($B24,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D24" s="12">
+        <f>IF($B24="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B24&amp;"#1",원장입력!$L$5:$L$204,0))="",$B24&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B24&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C24&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B24&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C24,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E24" s="15">
         <f>IF($B24="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B24))</f>
         <v/>
       </c>
-      <c r="E24" s="15">
+      <c r="F24" s="15">
         <f>IF($B24="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B24))</f>
         <v/>
       </c>
-      <c r="F24" s="15">
-        <f>IF($B24="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B24)+IF($C24=$B24,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C24)))</f>
-        <v/>
-      </c>
       <c r="G24" s="15">
-        <f>IF($B24="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B24)+IF($C24=$B24,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C24)))</f>
+        <f>IF($B24="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B24)+IF($D24=$B24,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D24)))</f>
         <v/>
       </c>
       <c r="H24" s="15">
-        <f>IF($B24="","",IF(OR($A24="자산",$A24="비용"),D24-E24+F24-G24,E24-D24+G24-F24))</f>
-        <v/>
-      </c>
-      <c r="I24" s="16" t="n"/>
+        <f>IF($B24="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B24)+IF($D24=$B24,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D24)))</f>
+        <v/>
+      </c>
+      <c r="I24" s="15">
+        <f>IF($B24="","",IF(OR($A24="자산",$A24="비용"),E24-F24+G24-H24,F24-E24+H24-G24))</f>
+        <v/>
+      </c>
+      <c r="J24" s="16" t="n"/>
+      <c r="K24" s="5">
+        <f>IF($B24="","",IFERROR(MATCH(--$B24,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B24,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="13">
-        <f>IF($B25="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C25,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B25="","",IF(AND($K25&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K25)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K25),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B25&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B25" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C25" s="12">
-        <f>IF($B25="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B25&amp;"#1",원장입력!$L$5:$L$204,0))="",$B25&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B25&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D25" s="15">
+      <c r="C25" s="13">
+        <f>IF($B25="","",IF(AND($K25&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K25)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K25),IF(LEFT($B25,1)="5","제조",IF(LEFT($B25,1)="6","도급",IF(LEFT($B25,1)="7","분양",IF(LEFT($B25,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D25" s="12">
+        <f>IF($B25="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B25&amp;"#1",원장입력!$L$5:$L$204,0))="",$B25&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B25&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C25&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B25&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C25,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E25" s="15">
         <f>IF($B25="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B25))</f>
         <v/>
       </c>
-      <c r="E25" s="15">
+      <c r="F25" s="15">
         <f>IF($B25="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B25))</f>
         <v/>
       </c>
-      <c r="F25" s="15">
-        <f>IF($B25="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B25)+IF($C25=$B25,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C25)))</f>
-        <v/>
-      </c>
       <c r="G25" s="15">
-        <f>IF($B25="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B25)+IF($C25=$B25,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C25)))</f>
+        <f>IF($B25="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B25)+IF($D25=$B25,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D25)))</f>
         <v/>
       </c>
       <c r="H25" s="15">
-        <f>IF($B25="","",IF(OR($A25="자산",$A25="비용"),D25-E25+F25-G25,E25-D25+G25-F25))</f>
-        <v/>
-      </c>
-      <c r="I25" s="16" t="n"/>
+        <f>IF($B25="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B25)+IF($D25=$B25,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D25)))</f>
+        <v/>
+      </c>
+      <c r="I25" s="15">
+        <f>IF($B25="","",IF(OR($A25="자산",$A25="비용"),E25-F25+G25-H25,F25-E25+H25-G25))</f>
+        <v/>
+      </c>
+      <c r="J25" s="16" t="n"/>
+      <c r="K25" s="5">
+        <f>IF($B25="","",IFERROR(MATCH(--$B25,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B25,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="13">
-        <f>IF($B26="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C26,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B26="","",IF(AND($K26&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K26)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K26),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B26&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B26" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C26" s="12">
-        <f>IF($B26="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B26&amp;"#1",원장입력!$L$5:$L$204,0))="",$B26&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B26&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D26" s="15">
+      <c r="C26" s="13">
+        <f>IF($B26="","",IF(AND($K26&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K26)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K26),IF(LEFT($B26,1)="5","제조",IF(LEFT($B26,1)="6","도급",IF(LEFT($B26,1)="7","분양",IF(LEFT($B26,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D26" s="12">
+        <f>IF($B26="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B26&amp;"#1",원장입력!$L$5:$L$204,0))="",$B26&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B26&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C26&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B26&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C26,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E26" s="15">
         <f>IF($B26="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B26))</f>
         <v/>
       </c>
-      <c r="E26" s="15">
+      <c r="F26" s="15">
         <f>IF($B26="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B26))</f>
         <v/>
       </c>
-      <c r="F26" s="15">
-        <f>IF($B26="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B26)+IF($C26=$B26,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C26)))</f>
-        <v/>
-      </c>
       <c r="G26" s="15">
-        <f>IF($B26="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B26)+IF($C26=$B26,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C26)))</f>
+        <f>IF($B26="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B26)+IF($D26=$B26,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D26)))</f>
         <v/>
       </c>
       <c r="H26" s="15">
-        <f>IF($B26="","",IF(OR($A26="자산",$A26="비용"),D26-E26+F26-G26,E26-D26+G26-F26))</f>
-        <v/>
-      </c>
-      <c r="I26" s="16" t="n"/>
+        <f>IF($B26="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B26)+IF($D26=$B26,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D26)))</f>
+        <v/>
+      </c>
+      <c r="I26" s="15">
+        <f>IF($B26="","",IF(OR($A26="자산",$A26="비용"),E26-F26+G26-H26,F26-E26+H26-G26))</f>
+        <v/>
+      </c>
+      <c r="J26" s="16" t="n"/>
+      <c r="K26" s="5">
+        <f>IF($B26="","",IFERROR(MATCH(--$B26,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B26,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="13">
-        <f>IF($B27="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C27,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B27="","",IF(AND($K27&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K27)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K27),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B27&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B27" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C27" s="12">
-        <f>IF($B27="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B27&amp;"#1",원장입력!$L$5:$L$204,0))="",$B27&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B27&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D27" s="15">
+      <c r="C27" s="13">
+        <f>IF($B27="","",IF(AND($K27&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K27)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K27),IF(LEFT($B27,1)="5","제조",IF(LEFT($B27,1)="6","도급",IF(LEFT($B27,1)="7","분양",IF(LEFT($B27,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D27" s="12">
+        <f>IF($B27="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B27&amp;"#1",원장입력!$L$5:$L$204,0))="",$B27&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B27&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C27&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B27&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C27,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E27" s="15">
         <f>IF($B27="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B27))</f>
         <v/>
       </c>
-      <c r="E27" s="15">
+      <c r="F27" s="15">
         <f>IF($B27="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B27))</f>
         <v/>
       </c>
-      <c r="F27" s="15">
-        <f>IF($B27="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B27)+IF($C27=$B27,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C27)))</f>
-        <v/>
-      </c>
       <c r="G27" s="15">
-        <f>IF($B27="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B27)+IF($C27=$B27,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C27)))</f>
+        <f>IF($B27="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B27)+IF($D27=$B27,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D27)))</f>
         <v/>
       </c>
       <c r="H27" s="15">
-        <f>IF($B27="","",IF(OR($A27="자산",$A27="비용"),D27-E27+F27-G27,E27-D27+G27-F27))</f>
-        <v/>
-      </c>
-      <c r="I27" s="16" t="n"/>
+        <f>IF($B27="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B27)+IF($D27=$B27,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D27)))</f>
+        <v/>
+      </c>
+      <c r="I27" s="15">
+        <f>IF($B27="","",IF(OR($A27="자산",$A27="비용"),E27-F27+G27-H27,F27-E27+H27-G27))</f>
+        <v/>
+      </c>
+      <c r="J27" s="16" t="n"/>
+      <c r="K27" s="5">
+        <f>IF($B27="","",IFERROR(MATCH(--$B27,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B27,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="13">
-        <f>IF($B28="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C28,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B28="","",IF(AND($K28&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K28)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K28),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B28&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B28" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C28" s="12">
-        <f>IF($B28="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B28&amp;"#1",원장입력!$L$5:$L$204,0))="",$B28&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B28&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D28" s="15">
+      <c r="C28" s="13">
+        <f>IF($B28="","",IF(AND($K28&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K28)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K28),IF(LEFT($B28,1)="5","제조",IF(LEFT($B28,1)="6","도급",IF(LEFT($B28,1)="7","분양",IF(LEFT($B28,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D28" s="12">
+        <f>IF($B28="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B28&amp;"#1",원장입력!$L$5:$L$204,0))="",$B28&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B28&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C28&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B28&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C28,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E28" s="15">
         <f>IF($B28="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B28))</f>
         <v/>
       </c>
-      <c r="E28" s="15">
+      <c r="F28" s="15">
         <f>IF($B28="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B28))</f>
         <v/>
       </c>
-      <c r="F28" s="15">
-        <f>IF($B28="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B28)+IF($C28=$B28,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C28)))</f>
-        <v/>
-      </c>
       <c r="G28" s="15">
-        <f>IF($B28="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B28)+IF($C28=$B28,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C28)))</f>
+        <f>IF($B28="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B28)+IF($D28=$B28,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D28)))</f>
         <v/>
       </c>
       <c r="H28" s="15">
-        <f>IF($B28="","",IF(OR($A28="자산",$A28="비용"),D28-E28+F28-G28,E28-D28+G28-F28))</f>
-        <v/>
-      </c>
-      <c r="I28" s="16" t="n"/>
+        <f>IF($B28="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B28)+IF($D28=$B28,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D28)))</f>
+        <v/>
+      </c>
+      <c r="I28" s="15">
+        <f>IF($B28="","",IF(OR($A28="자산",$A28="비용"),E28-F28+G28-H28,F28-E28+H28-G28))</f>
+        <v/>
+      </c>
+      <c r="J28" s="16" t="n"/>
+      <c r="K28" s="5">
+        <f>IF($B28="","",IFERROR(MATCH(--$B28,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B28,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="13">
-        <f>IF($B29="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C29,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B29="","",IF(AND($K29&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K29)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K29),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B29&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B29" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C29" s="12">
-        <f>IF($B29="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B29&amp;"#1",원장입력!$L$5:$L$204,0))="",$B29&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B29&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D29" s="15">
+      <c r="C29" s="13">
+        <f>IF($B29="","",IF(AND($K29&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K29)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K29),IF(LEFT($B29,1)="5","제조",IF(LEFT($B29,1)="6","도급",IF(LEFT($B29,1)="7","분양",IF(LEFT($B29,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D29" s="12">
+        <f>IF($B29="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B29&amp;"#1",원장입력!$L$5:$L$204,0))="",$B29&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B29&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C29&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B29&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C29,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E29" s="15">
         <f>IF($B29="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B29))</f>
         <v/>
       </c>
-      <c r="E29" s="15">
+      <c r="F29" s="15">
         <f>IF($B29="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B29))</f>
         <v/>
       </c>
-      <c r="F29" s="15">
-        <f>IF($B29="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B29)+IF($C29=$B29,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C29)))</f>
-        <v/>
-      </c>
       <c r="G29" s="15">
-        <f>IF($B29="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B29)+IF($C29=$B29,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C29)))</f>
+        <f>IF($B29="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B29)+IF($D29=$B29,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D29)))</f>
         <v/>
       </c>
       <c r="H29" s="15">
-        <f>IF($B29="","",IF(OR($A29="자산",$A29="비용"),D29-E29+F29-G29,E29-D29+G29-F29))</f>
-        <v/>
-      </c>
-      <c r="I29" s="16" t="n"/>
+        <f>IF($B29="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B29)+IF($D29=$B29,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D29)))</f>
+        <v/>
+      </c>
+      <c r="I29" s="15">
+        <f>IF($B29="","",IF(OR($A29="자산",$A29="비용"),E29-F29+G29-H29,F29-E29+H29-G29))</f>
+        <v/>
+      </c>
+      <c r="J29" s="16" t="n"/>
+      <c r="K29" s="5">
+        <f>IF($B29="","",IFERROR(MATCH(--$B29,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B29,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="13">
-        <f>IF($B30="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C30,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B30="","",IF(AND($K30&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K30)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K30),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B30&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B30" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C30" s="12">
-        <f>IF($B30="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B30&amp;"#1",원장입력!$L$5:$L$204,0))="",$B30&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B30&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D30" s="15">
+      <c r="C30" s="13">
+        <f>IF($B30="","",IF(AND($K30&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K30)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K30),IF(LEFT($B30,1)="5","제조",IF(LEFT($B30,1)="6","도급",IF(LEFT($B30,1)="7","분양",IF(LEFT($B30,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D30" s="12">
+        <f>IF($B30="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B30&amp;"#1",원장입력!$L$5:$L$204,0))="",$B30&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B30&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C30&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B30&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C30,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E30" s="15">
         <f>IF($B30="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B30))</f>
         <v/>
       </c>
-      <c r="E30" s="15">
+      <c r="F30" s="15">
         <f>IF($B30="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B30))</f>
         <v/>
       </c>
-      <c r="F30" s="15">
-        <f>IF($B30="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B30)+IF($C30=$B30,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C30)))</f>
-        <v/>
-      </c>
       <c r="G30" s="15">
-        <f>IF($B30="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B30)+IF($C30=$B30,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C30)))</f>
+        <f>IF($B30="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B30)+IF($D30=$B30,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D30)))</f>
         <v/>
       </c>
       <c r="H30" s="15">
-        <f>IF($B30="","",IF(OR($A30="자산",$A30="비용"),D30-E30+F30-G30,E30-D30+G30-F30))</f>
-        <v/>
-      </c>
-      <c r="I30" s="16" t="n"/>
+        <f>IF($B30="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B30)+IF($D30=$B30,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D30)))</f>
+        <v/>
+      </c>
+      <c r="I30" s="15">
+        <f>IF($B30="","",IF(OR($A30="자산",$A30="비용"),E30-F30+G30-H30,F30-E30+H30-G30))</f>
+        <v/>
+      </c>
+      <c r="J30" s="16" t="n"/>
+      <c r="K30" s="5">
+        <f>IF($B30="","",IFERROR(MATCH(--$B30,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B30,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="13">
-        <f>IF($B31="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C31,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B31="","",IF(AND($K31&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K31)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K31),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B31&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B31" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C31" s="12">
-        <f>IF($B31="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B31&amp;"#1",원장입력!$L$5:$L$204,0))="",$B31&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B31&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D31" s="15">
+      <c r="C31" s="13">
+        <f>IF($B31="","",IF(AND($K31&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K31)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K31),IF(LEFT($B31,1)="5","제조",IF(LEFT($B31,1)="6","도급",IF(LEFT($B31,1)="7","분양",IF(LEFT($B31,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D31" s="12">
+        <f>IF($B31="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B31&amp;"#1",원장입력!$L$5:$L$204,0))="",$B31&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B31&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C31&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B31&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C31,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E31" s="15">
         <f>IF($B31="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B31))</f>
         <v/>
       </c>
-      <c r="E31" s="15">
+      <c r="F31" s="15">
         <f>IF($B31="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B31))</f>
         <v/>
       </c>
-      <c r="F31" s="15">
-        <f>IF($B31="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B31)+IF($C31=$B31,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C31)))</f>
-        <v/>
-      </c>
       <c r="G31" s="15">
-        <f>IF($B31="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B31)+IF($C31=$B31,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C31)))</f>
+        <f>IF($B31="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B31)+IF($D31=$B31,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D31)))</f>
         <v/>
       </c>
       <c r="H31" s="15">
-        <f>IF($B31="","",IF(OR($A31="자산",$A31="비용"),D31-E31+F31-G31,E31-D31+G31-F31))</f>
-        <v/>
-      </c>
-      <c r="I31" s="16" t="n"/>
+        <f>IF($B31="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B31)+IF($D31=$B31,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D31)))</f>
+        <v/>
+      </c>
+      <c r="I31" s="15">
+        <f>IF($B31="","",IF(OR($A31="자산",$A31="비용"),E31-F31+G31-H31,F31-E31+H31-G31))</f>
+        <v/>
+      </c>
+      <c r="J31" s="16" t="n"/>
+      <c r="K31" s="5">
+        <f>IF($B31="","",IFERROR(MATCH(--$B31,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B31,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="13">
-        <f>IF($B32="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C32,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B32="","",IF(AND($K32&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K32)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K32),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B32&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B32" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C32" s="12">
-        <f>IF($B32="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B32&amp;"#1",원장입력!$L$5:$L$204,0))="",$B32&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B32&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D32" s="15">
+      <c r="C32" s="13">
+        <f>IF($B32="","",IF(AND($K32&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K32)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K32),IF(LEFT($B32,1)="5","제조",IF(LEFT($B32,1)="6","도급",IF(LEFT($B32,1)="7","분양",IF(LEFT($B32,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D32" s="12">
+        <f>IF($B32="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B32&amp;"#1",원장입력!$L$5:$L$204,0))="",$B32&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B32&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C32&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B32&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C32,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E32" s="15">
         <f>IF($B32="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B32))</f>
         <v/>
       </c>
-      <c r="E32" s="15">
+      <c r="F32" s="15">
         <f>IF($B32="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B32))</f>
         <v/>
       </c>
-      <c r="F32" s="15">
-        <f>IF($B32="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B32)+IF($C32=$B32,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C32)))</f>
-        <v/>
-      </c>
       <c r="G32" s="15">
-        <f>IF($B32="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B32)+IF($C32=$B32,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C32)))</f>
+        <f>IF($B32="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B32)+IF($D32=$B32,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D32)))</f>
         <v/>
       </c>
       <c r="H32" s="15">
-        <f>IF($B32="","",IF(OR($A32="자산",$A32="비용"),D32-E32+F32-G32,E32-D32+G32-F32))</f>
-        <v/>
-      </c>
-      <c r="I32" s="16" t="n"/>
+        <f>IF($B32="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B32)+IF($D32=$B32,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D32)))</f>
+        <v/>
+      </c>
+      <c r="I32" s="15">
+        <f>IF($B32="","",IF(OR($A32="자산",$A32="비용"),E32-F32+G32-H32,F32-E32+H32-G32))</f>
+        <v/>
+      </c>
+      <c r="J32" s="16" t="n"/>
+      <c r="K32" s="5">
+        <f>IF($B32="","",IFERROR(MATCH(--$B32,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B32,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="13">
-        <f>IF($B33="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C33,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B33="","",IF(AND($K33&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K33)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K33),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B33&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B33" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C33" s="12">
-        <f>IF($B33="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B33&amp;"#1",원장입력!$L$5:$L$204,0))="",$B33&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B33&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D33" s="15">
+      <c r="C33" s="13">
+        <f>IF($B33="","",IF(AND($K33&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K33)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K33),IF(LEFT($B33,1)="5","제조",IF(LEFT($B33,1)="6","도급",IF(LEFT($B33,1)="7","분양",IF(LEFT($B33,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D33" s="12">
+        <f>IF($B33="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B33&amp;"#1",원장입력!$L$5:$L$204,0))="",$B33&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B33&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C33&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B33&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C33,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E33" s="15">
         <f>IF($B33="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B33))</f>
         <v/>
       </c>
-      <c r="E33" s="15">
+      <c r="F33" s="15">
         <f>IF($B33="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B33))</f>
         <v/>
       </c>
-      <c r="F33" s="15">
-        <f>IF($B33="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B33)+IF($C33=$B33,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C33)))</f>
-        <v/>
-      </c>
       <c r="G33" s="15">
-        <f>IF($B33="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B33)+IF($C33=$B33,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C33)))</f>
+        <f>IF($B33="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B33)+IF($D33=$B33,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D33)))</f>
         <v/>
       </c>
       <c r="H33" s="15">
-        <f>IF($B33="","",IF(OR($A33="자산",$A33="비용"),D33-E33+F33-G33,E33-D33+G33-F33))</f>
-        <v/>
-      </c>
-      <c r="I33" s="16" t="n"/>
+        <f>IF($B33="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B33)+IF($D33=$B33,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D33)))</f>
+        <v/>
+      </c>
+      <c r="I33" s="15">
+        <f>IF($B33="","",IF(OR($A33="자산",$A33="비용"),E33-F33+G33-H33,F33-E33+H33-G33))</f>
+        <v/>
+      </c>
+      <c r="J33" s="16" t="n"/>
+      <c r="K33" s="5">
+        <f>IF($B33="","",IFERROR(MATCH(--$B33,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B33,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="13">
-        <f>IF($B34="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C34,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B34="","",IF(AND($K34&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K34)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K34),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B34&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B34" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C34" s="12">
-        <f>IF($B34="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B34&amp;"#1",원장입력!$L$5:$L$204,0))="",$B34&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B34&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D34" s="15">
+      <c r="C34" s="13">
+        <f>IF($B34="","",IF(AND($K34&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K34)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K34),IF(LEFT($B34,1)="5","제조",IF(LEFT($B34,1)="6","도급",IF(LEFT($B34,1)="7","분양",IF(LEFT($B34,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D34" s="12">
+        <f>IF($B34="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B34&amp;"#1",원장입력!$L$5:$L$204,0))="",$B34&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B34&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C34&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B34&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C34,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E34" s="15">
         <f>IF($B34="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B34))</f>
         <v/>
       </c>
-      <c r="E34" s="15">
+      <c r="F34" s="15">
         <f>IF($B34="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B34))</f>
         <v/>
       </c>
-      <c r="F34" s="15">
-        <f>IF($B34="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B34)+IF($C34=$B34,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C34)))</f>
-        <v/>
-      </c>
       <c r="G34" s="15">
-        <f>IF($B34="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B34)+IF($C34=$B34,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C34)))</f>
+        <f>IF($B34="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B34)+IF($D34=$B34,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D34)))</f>
         <v/>
       </c>
       <c r="H34" s="15">
-        <f>IF($B34="","",IF(OR($A34="자산",$A34="비용"),D34-E34+F34-G34,E34-D34+G34-F34))</f>
-        <v/>
-      </c>
-      <c r="I34" s="16" t="n"/>
+        <f>IF($B34="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B34)+IF($D34=$B34,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D34)))</f>
+        <v/>
+      </c>
+      <c r="I34" s="15">
+        <f>IF($B34="","",IF(OR($A34="자산",$A34="비용"),E34-F34+G34-H34,F34-E34+H34-G34))</f>
+        <v/>
+      </c>
+      <c r="J34" s="16" t="n"/>
+      <c r="K34" s="5">
+        <f>IF($B34="","",IFERROR(MATCH(--$B34,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B34,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="13">
-        <f>IF($B35="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C35,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B35="","",IF(AND($K35&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K35)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K35),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B35&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B35" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C35" s="12">
-        <f>IF($B35="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B35&amp;"#1",원장입력!$L$5:$L$204,0))="",$B35&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B35&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D35" s="15">
+      <c r="C35" s="13">
+        <f>IF($B35="","",IF(AND($K35&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K35)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K35),IF(LEFT($B35,1)="5","제조",IF(LEFT($B35,1)="6","도급",IF(LEFT($B35,1)="7","분양",IF(LEFT($B35,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D35" s="12">
+        <f>IF($B35="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B35&amp;"#1",원장입력!$L$5:$L$204,0))="",$B35&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B35&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C35&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B35&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C35,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E35" s="15">
         <f>IF($B35="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B35))</f>
         <v/>
       </c>
-      <c r="E35" s="15">
+      <c r="F35" s="15">
         <f>IF($B35="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B35))</f>
         <v/>
       </c>
-      <c r="F35" s="15">
-        <f>IF($B35="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B35)+IF($C35=$B35,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C35)))</f>
-        <v/>
-      </c>
       <c r="G35" s="15">
-        <f>IF($B35="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B35)+IF($C35=$B35,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C35)))</f>
+        <f>IF($B35="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B35)+IF($D35=$B35,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D35)))</f>
         <v/>
       </c>
       <c r="H35" s="15">
-        <f>IF($B35="","",IF(OR($A35="자산",$A35="비용"),D35-E35+F35-G35,E35-D35+G35-F35))</f>
-        <v/>
-      </c>
-      <c r="I35" s="16" t="n"/>
+        <f>IF($B35="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B35)+IF($D35=$B35,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D35)))</f>
+        <v/>
+      </c>
+      <c r="I35" s="15">
+        <f>IF($B35="","",IF(OR($A35="자산",$A35="비용"),E35-F35+G35-H35,F35-E35+H35-G35))</f>
+        <v/>
+      </c>
+      <c r="J35" s="16" t="n"/>
+      <c r="K35" s="5">
+        <f>IF($B35="","",IFERROR(MATCH(--$B35,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B35,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="13">
-        <f>IF($B36="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C36,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B36="","",IF(AND($K36&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K36)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K36),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B36&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B36" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C36" s="12">
-        <f>IF($B36="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B36&amp;"#1",원장입력!$L$5:$L$204,0))="",$B36&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B36&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D36" s="15">
+      <c r="C36" s="13">
+        <f>IF($B36="","",IF(AND($K36&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K36)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K36),IF(LEFT($B36,1)="5","제조",IF(LEFT($B36,1)="6","도급",IF(LEFT($B36,1)="7","분양",IF(LEFT($B36,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D36" s="12">
+        <f>IF($B36="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B36&amp;"#1",원장입력!$L$5:$L$204,0))="",$B36&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B36&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C36&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B36&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C36,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E36" s="15">
         <f>IF($B36="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B36))</f>
         <v/>
       </c>
-      <c r="E36" s="15">
+      <c r="F36" s="15">
         <f>IF($B36="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B36))</f>
         <v/>
       </c>
-      <c r="F36" s="15">
-        <f>IF($B36="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B36)+IF($C36=$B36,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C36)))</f>
-        <v/>
-      </c>
       <c r="G36" s="15">
-        <f>IF($B36="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B36)+IF($C36=$B36,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C36)))</f>
+        <f>IF($B36="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B36)+IF($D36=$B36,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D36)))</f>
         <v/>
       </c>
       <c r="H36" s="15">
-        <f>IF($B36="","",IF(OR($A36="자산",$A36="비용"),D36-E36+F36-G36,E36-D36+G36-F36))</f>
-        <v/>
-      </c>
-      <c r="I36" s="16" t="n"/>
+        <f>IF($B36="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B36)+IF($D36=$B36,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D36)))</f>
+        <v/>
+      </c>
+      <c r="I36" s="15">
+        <f>IF($B36="","",IF(OR($A36="자산",$A36="비용"),E36-F36+G36-H36,F36-E36+H36-G36))</f>
+        <v/>
+      </c>
+      <c r="J36" s="16" t="n"/>
+      <c r="K36" s="5">
+        <f>IF($B36="","",IFERROR(MATCH(--$B36,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B36,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="13">
-        <f>IF($B37="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C37,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B37="","",IF(AND($K37&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K37)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K37),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B37&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B37" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C37" s="12">
-        <f>IF($B37="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B37&amp;"#1",원장입력!$L$5:$L$204,0))="",$B37&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B37&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D37" s="15">
+      <c r="C37" s="13">
+        <f>IF($B37="","",IF(AND($K37&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K37)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K37),IF(LEFT($B37,1)="5","제조",IF(LEFT($B37,1)="6","도급",IF(LEFT($B37,1)="7","분양",IF(LEFT($B37,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D37" s="12">
+        <f>IF($B37="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B37&amp;"#1",원장입력!$L$5:$L$204,0))="",$B37&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B37&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C37&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B37&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C37,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E37" s="15">
         <f>IF($B37="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B37))</f>
         <v/>
       </c>
-      <c r="E37" s="15">
+      <c r="F37" s="15">
         <f>IF($B37="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B37))</f>
         <v/>
       </c>
-      <c r="F37" s="15">
-        <f>IF($B37="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B37)+IF($C37=$B37,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C37)))</f>
-        <v/>
-      </c>
       <c r="G37" s="15">
-        <f>IF($B37="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B37)+IF($C37=$B37,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C37)))</f>
+        <f>IF($B37="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B37)+IF($D37=$B37,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D37)))</f>
         <v/>
       </c>
       <c r="H37" s="15">
-        <f>IF($B37="","",IF(OR($A37="자산",$A37="비용"),D37-E37+F37-G37,E37-D37+G37-F37))</f>
-        <v/>
-      </c>
-      <c r="I37" s="16" t="n"/>
+        <f>IF($B37="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B37)+IF($D37=$B37,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D37)))</f>
+        <v/>
+      </c>
+      <c r="I37" s="15">
+        <f>IF($B37="","",IF(OR($A37="자산",$A37="비용"),E37-F37+G37-H37,F37-E37+H37-G37))</f>
+        <v/>
+      </c>
+      <c r="J37" s="16" t="n"/>
+      <c r="K37" s="5">
+        <f>IF($B37="","",IFERROR(MATCH(--$B37,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B37,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="13">
-        <f>IF($B38="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C38,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B38="","",IF(AND($K38&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K38)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K38),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B38&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B38" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C38" s="12">
-        <f>IF($B38="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B38&amp;"#1",원장입력!$L$5:$L$204,0))="",$B38&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B38&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D38" s="15">
+      <c r="C38" s="13">
+        <f>IF($B38="","",IF(AND($K38&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K38)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K38),IF(LEFT($B38,1)="5","제조",IF(LEFT($B38,1)="6","도급",IF(LEFT($B38,1)="7","분양",IF(LEFT($B38,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D38" s="12">
+        <f>IF($B38="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B38&amp;"#1",원장입력!$L$5:$L$204,0))="",$B38&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B38&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C38&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B38&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C38,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E38" s="15">
         <f>IF($B38="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B38))</f>
         <v/>
       </c>
-      <c r="E38" s="15">
+      <c r="F38" s="15">
         <f>IF($B38="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B38))</f>
         <v/>
       </c>
-      <c r="F38" s="15">
-        <f>IF($B38="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B38)+IF($C38=$B38,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C38)))</f>
-        <v/>
-      </c>
       <c r="G38" s="15">
-        <f>IF($B38="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B38)+IF($C38=$B38,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C38)))</f>
+        <f>IF($B38="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B38)+IF($D38=$B38,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D38)))</f>
         <v/>
       </c>
       <c r="H38" s="15">
-        <f>IF($B38="","",IF(OR($A38="자산",$A38="비용"),D38-E38+F38-G38,E38-D38+G38-F38))</f>
-        <v/>
-      </c>
-      <c r="I38" s="16" t="n"/>
+        <f>IF($B38="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B38)+IF($D38=$B38,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D38)))</f>
+        <v/>
+      </c>
+      <c r="I38" s="15">
+        <f>IF($B38="","",IF(OR($A38="자산",$A38="비용"),E38-F38+G38-H38,F38-E38+H38-G38))</f>
+        <v/>
+      </c>
+      <c r="J38" s="16" t="n"/>
+      <c r="K38" s="5">
+        <f>IF($B38="","",IFERROR(MATCH(--$B38,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B38,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="13">
-        <f>IF($B39="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C39,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B39="","",IF(AND($K39&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K39)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K39),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B39&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B39" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C39" s="12">
-        <f>IF($B39="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B39&amp;"#1",원장입력!$L$5:$L$204,0))="",$B39&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B39&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D39" s="15">
+      <c r="C39" s="13">
+        <f>IF($B39="","",IF(AND($K39&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K39)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K39),IF(LEFT($B39,1)="5","제조",IF(LEFT($B39,1)="6","도급",IF(LEFT($B39,1)="7","분양",IF(LEFT($B39,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D39" s="12">
+        <f>IF($B39="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B39&amp;"#1",원장입력!$L$5:$L$204,0))="",$B39&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B39&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C39&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B39&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C39,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E39" s="15">
         <f>IF($B39="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B39))</f>
         <v/>
       </c>
-      <c r="E39" s="15">
+      <c r="F39" s="15">
         <f>IF($B39="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B39))</f>
         <v/>
       </c>
-      <c r="F39" s="15">
-        <f>IF($B39="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B39)+IF($C39=$B39,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C39)))</f>
-        <v/>
-      </c>
       <c r="G39" s="15">
-        <f>IF($B39="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B39)+IF($C39=$B39,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C39)))</f>
+        <f>IF($B39="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B39)+IF($D39=$B39,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D39)))</f>
         <v/>
       </c>
       <c r="H39" s="15">
-        <f>IF($B39="","",IF(OR($A39="자산",$A39="비용"),D39-E39+F39-G39,E39-D39+G39-F39))</f>
-        <v/>
-      </c>
-      <c r="I39" s="16" t="n"/>
+        <f>IF($B39="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B39)+IF($D39=$B39,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D39)))</f>
+        <v/>
+      </c>
+      <c r="I39" s="15">
+        <f>IF($B39="","",IF(OR($A39="자산",$A39="비용"),E39-F39+G39-H39,F39-E39+H39-G39))</f>
+        <v/>
+      </c>
+      <c r="J39" s="16" t="n"/>
+      <c r="K39" s="5">
+        <f>IF($B39="","",IFERROR(MATCH(--$B39,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B39,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="13">
-        <f>IF($B40="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C40,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B40="","",IF(AND($K40&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K40)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K40),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B40&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B40" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C40" s="12">
-        <f>IF($B40="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B40&amp;"#1",원장입력!$L$5:$L$204,0))="",$B40&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B40&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D40" s="15">
+      <c r="C40" s="13">
+        <f>IF($B40="","",IF(AND($K40&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K40)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K40),IF(LEFT($B40,1)="5","제조",IF(LEFT($B40,1)="6","도급",IF(LEFT($B40,1)="7","분양",IF(LEFT($B40,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D40" s="12">
+        <f>IF($B40="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B40&amp;"#1",원장입력!$L$5:$L$204,0))="",$B40&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B40&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C40&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B40&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C40,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E40" s="15">
         <f>IF($B40="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B40))</f>
         <v/>
       </c>
-      <c r="E40" s="15">
+      <c r="F40" s="15">
         <f>IF($B40="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B40))</f>
         <v/>
       </c>
-      <c r="F40" s="15">
-        <f>IF($B40="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B40)+IF($C40=$B40,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C40)))</f>
-        <v/>
-      </c>
       <c r="G40" s="15">
-        <f>IF($B40="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B40)+IF($C40=$B40,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C40)))</f>
+        <f>IF($B40="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B40)+IF($D40=$B40,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D40)))</f>
         <v/>
       </c>
       <c r="H40" s="15">
-        <f>IF($B40="","",IF(OR($A40="자산",$A40="비용"),D40-E40+F40-G40,E40-D40+G40-F40))</f>
-        <v/>
-      </c>
-      <c r="I40" s="16" t="n"/>
+        <f>IF($B40="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B40)+IF($D40=$B40,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D40)))</f>
+        <v/>
+      </c>
+      <c r="I40" s="15">
+        <f>IF($B40="","",IF(OR($A40="자산",$A40="비용"),E40-F40+G40-H40,F40-E40+H40-G40))</f>
+        <v/>
+      </c>
+      <c r="J40" s="16" t="n"/>
+      <c r="K40" s="5">
+        <f>IF($B40="","",IFERROR(MATCH(--$B40,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B40,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="13">
-        <f>IF($B41="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C41,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B41="","",IF(AND($K41&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K41)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K41),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B41&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B41" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C41" s="12">
-        <f>IF($B41="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B41&amp;"#1",원장입력!$L$5:$L$204,0))="",$B41&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B41&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D41" s="15">
+      <c r="C41" s="13">
+        <f>IF($B41="","",IF(AND($K41&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K41)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K41),IF(LEFT($B41,1)="5","제조",IF(LEFT($B41,1)="6","도급",IF(LEFT($B41,1)="7","분양",IF(LEFT($B41,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D41" s="12">
+        <f>IF($B41="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B41&amp;"#1",원장입력!$L$5:$L$204,0))="",$B41&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B41&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C41&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B41&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C41,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E41" s="15">
         <f>IF($B41="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B41))</f>
         <v/>
       </c>
-      <c r="E41" s="15">
+      <c r="F41" s="15">
         <f>IF($B41="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B41))</f>
         <v/>
       </c>
-      <c r="F41" s="15">
-        <f>IF($B41="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B41)+IF($C41=$B41,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C41)))</f>
-        <v/>
-      </c>
       <c r="G41" s="15">
-        <f>IF($B41="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B41)+IF($C41=$B41,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C41)))</f>
+        <f>IF($B41="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B41)+IF($D41=$B41,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D41)))</f>
         <v/>
       </c>
       <c r="H41" s="15">
-        <f>IF($B41="","",IF(OR($A41="자산",$A41="비용"),D41-E41+F41-G41,E41-D41+G41-F41))</f>
-        <v/>
-      </c>
-      <c r="I41" s="16" t="n"/>
+        <f>IF($B41="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B41)+IF($D41=$B41,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D41)))</f>
+        <v/>
+      </c>
+      <c r="I41" s="15">
+        <f>IF($B41="","",IF(OR($A41="자산",$A41="비용"),E41-F41+G41-H41,F41-E41+H41-G41))</f>
+        <v/>
+      </c>
+      <c r="J41" s="16" t="n"/>
+      <c r="K41" s="5">
+        <f>IF($B41="","",IFERROR(MATCH(--$B41,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B41,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="13">
-        <f>IF($B42="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C42,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B42="","",IF(AND($K42&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K42)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K42),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B42&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B42" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C42" s="12">
-        <f>IF($B42="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B42&amp;"#1",원장입력!$L$5:$L$204,0))="",$B42&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B42&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D42" s="15">
+      <c r="C42" s="13">
+        <f>IF($B42="","",IF(AND($K42&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K42)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K42),IF(LEFT($B42,1)="5","제조",IF(LEFT($B42,1)="6","도급",IF(LEFT($B42,1)="7","분양",IF(LEFT($B42,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D42" s="12">
+        <f>IF($B42="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B42&amp;"#1",원장입력!$L$5:$L$204,0))="",$B42&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B42&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C42&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B42&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C42,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E42" s="15">
         <f>IF($B42="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B42))</f>
         <v/>
       </c>
-      <c r="E42" s="15">
+      <c r="F42" s="15">
         <f>IF($B42="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B42))</f>
         <v/>
       </c>
-      <c r="F42" s="15">
-        <f>IF($B42="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B42)+IF($C42=$B42,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C42)))</f>
-        <v/>
-      </c>
       <c r="G42" s="15">
-        <f>IF($B42="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B42)+IF($C42=$B42,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C42)))</f>
+        <f>IF($B42="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B42)+IF($D42=$B42,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D42)))</f>
         <v/>
       </c>
       <c r="H42" s="15">
-        <f>IF($B42="","",IF(OR($A42="자산",$A42="비용"),D42-E42+F42-G42,E42-D42+G42-F42))</f>
-        <v/>
-      </c>
-      <c r="I42" s="16" t="n"/>
+        <f>IF($B42="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B42)+IF($D42=$B42,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D42)))</f>
+        <v/>
+      </c>
+      <c r="I42" s="15">
+        <f>IF($B42="","",IF(OR($A42="자산",$A42="비용"),E42-F42+G42-H42,F42-E42+H42-G42))</f>
+        <v/>
+      </c>
+      <c r="J42" s="16" t="n"/>
+      <c r="K42" s="5">
+        <f>IF($B42="","",IFERROR(MATCH(--$B42,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B42,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="13">
-        <f>IF($B43="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C43,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B43="","",IF(AND($K43&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K43)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K43),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B43&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B43" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C43" s="12">
-        <f>IF($B43="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B43&amp;"#1",원장입력!$L$5:$L$204,0))="",$B43&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B43&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D43" s="15">
+      <c r="C43" s="13">
+        <f>IF($B43="","",IF(AND($K43&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K43)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K43),IF(LEFT($B43,1)="5","제조",IF(LEFT($B43,1)="6","도급",IF(LEFT($B43,1)="7","분양",IF(LEFT($B43,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D43" s="12">
+        <f>IF($B43="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B43&amp;"#1",원장입력!$L$5:$L$204,0))="",$B43&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B43&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C43&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B43&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C43,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E43" s="15">
         <f>IF($B43="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B43))</f>
         <v/>
       </c>
-      <c r="E43" s="15">
+      <c r="F43" s="15">
         <f>IF($B43="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B43))</f>
         <v/>
       </c>
-      <c r="F43" s="15">
-        <f>IF($B43="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B43)+IF($C43=$B43,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C43)))</f>
-        <v/>
-      </c>
       <c r="G43" s="15">
-        <f>IF($B43="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B43)+IF($C43=$B43,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C43)))</f>
+        <f>IF($B43="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B43)+IF($D43=$B43,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D43)))</f>
         <v/>
       </c>
       <c r="H43" s="15">
-        <f>IF($B43="","",IF(OR($A43="자산",$A43="비용"),D43-E43+F43-G43,E43-D43+G43-F43))</f>
-        <v/>
-      </c>
-      <c r="I43" s="16" t="n"/>
+        <f>IF($B43="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B43)+IF($D43=$B43,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D43)))</f>
+        <v/>
+      </c>
+      <c r="I43" s="15">
+        <f>IF($B43="","",IF(OR($A43="자산",$A43="비용"),E43-F43+G43-H43,F43-E43+H43-G43))</f>
+        <v/>
+      </c>
+      <c r="J43" s="16" t="n"/>
+      <c r="K43" s="5">
+        <f>IF($B43="","",IFERROR(MATCH(--$B43,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B43,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="13">
-        <f>IF($B44="","",IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH($C44,계정분류!$A$5:$A$101,0)),"미분류"))</f>
+        <f>IF($B44="","",IF(AND($K44&lt;&gt;"",INDEX(코드매핑!$E$5:$E$104,$K44)&lt;&gt;""),INDEX(코드매핑!$E$5:$E$104,$K44),IFERROR(INDEX(계정분류!$B$5:$B$101,MATCH(INDEX(원장입력!$J$5:$J$204,MATCH($B44&amp;"#1",원장입력!$L$5:$L$204,0)),계정분류!$A$5:$A$101,0)),"미분류")))</f>
         <v/>
       </c>
       <c r="B44" s="12">
         <f>IFERROR(INDEX(원장입력!$I$5:$I$204,MATCH(ROW()-4,원장입력!$M$5:$M$204,0)),"")</f>
         <v/>
       </c>
-      <c r="C44" s="12">
-        <f>IF($B44="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B44&amp;"#1",원장입력!$L$5:$L$204,0))="",$B44&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B44&amp;"#1",원장입력!$L$5:$L$204,0))))</f>
-        <v/>
-      </c>
-      <c r="D44" s="15">
+      <c r="C44" s="13">
+        <f>IF($B44="","",IF(AND($K44&lt;&gt;"",INDEX(코드매핑!$F$5:$F$104,$K44)&lt;&gt;""),INDEX(코드매핑!$F$5:$F$104,$K44),IF(LEFT($B44,1)="5","제조",IF(LEFT($B44,1)="6","도급",IF(LEFT($B44,1)="7","분양",IF(LEFT($B44,1)="8","판관",""))))))</f>
+        <v/>
+      </c>
+      <c r="D44" s="12">
+        <f>IF($B44="","",IF(INDEX(원장입력!$J$5:$J$204,MATCH($B44&amp;"#1",원장입력!$L$5:$L$204,0))="",$B44&amp;"",INDEX(원장입력!$J$5:$J$204,MATCH($B44&amp;"#1",원장입력!$L$5:$L$204,0))&amp;IF(AND($C44&lt;&gt;"",ISERROR(FIND("(",INDEX(원장입력!$J$5:$J$204,MATCH($B44&amp;"#1",원장입력!$L$5:$L$204,0)))))," ("&amp;LEFT($C44,1)&amp;")","")))</f>
+        <v/>
+      </c>
+      <c r="E44" s="15">
         <f>IF($B44="","",SUMIFS(원장입력!$G$5:$G$204,원장입력!$I$5:$I$204,$B44))</f>
         <v/>
       </c>
-      <c r="E44" s="15">
+      <c r="F44" s="15">
         <f>IF($B44="","",SUMIFS(원장입력!$H$5:$H$204,원장입력!$I$5:$I$204,$B44))</f>
         <v/>
       </c>
-      <c r="F44" s="15">
-        <f>IF($B44="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B44)+IF($C44=$B44,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$C44)))</f>
-        <v/>
-      </c>
       <c r="G44" s="15">
-        <f>IF($B44="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B44)+IF($C44=$B44,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$C44)))</f>
+        <f>IF($B44="","",SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$B44)+IF($D44=$B44,0,SUMIFS(결산조정!$B$5:$B$104,결산조정!$A$5:$A$104,$D44)))</f>
         <v/>
       </c>
       <c r="H44" s="15">
-        <f>IF($B44="","",IF(OR($A44="자산",$A44="비용"),D44-E44+F44-G44,E44-D44+G44-F44))</f>
-        <v/>
-      </c>
-      <c r="I44" s="16" t="n"/>
+        <f>IF($B44="","",SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$B44)+IF($D44=$B44,0,SUMIFS(결산조정!$C$5:$C$104,결산조정!$A$5:$A$104,$D44)))</f>
+        <v/>
+      </c>
+      <c r="I44" s="15">
+        <f>IF($B44="","",IF(OR($A44="자산",$A44="비용"),E44-F44+G44-H44,F44-E44+H44-G44))</f>
+        <v/>
+      </c>
+      <c r="J44" s="16" t="n"/>
+      <c r="K44" s="5">
+        <f>IF($B44="","",IFERROR(MATCH(--$B44,코드매핑!$A$5:$A$104,0),IFERROR(MATCH($B44,코드매핑!$A$5:$A$104,0),"")))</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13837,11 +14463,11 @@
         <v/>
       </c>
       <c r="B5" s="12">
-        <f>IF(결산명세서!$B5="","",결산명세서!$C5)</f>
+        <f>IF(결산명세서!$B5="","",결산명세서!$D5)</f>
         <v/>
       </c>
       <c r="C5" s="17">
-        <f>IF($B5="","",결산명세서!$H5)</f>
+        <f>IF($B5="","",결산명세서!$I5)</f>
         <v/>
       </c>
       <c r="D5" s="8" t="n">
@@ -13851,15 +14477,15 @@
         <v>500000</v>
       </c>
       <c r="F5" s="15">
-        <f>IF($B5="","",C5-D5)</f>
+        <f>IF(OR($B5="",$A5="수익",$A5="비용"),"",C5-D5)</f>
         <v/>
       </c>
       <c r="G5" s="15">
-        <f>IF($B5="","",D5-E5)</f>
+        <f>IF(OR($B5="",$A5="수익",$A5="비용"),"",D5-E5)</f>
         <v/>
       </c>
       <c r="H5" s="13">
-        <f>IF($B5="","",IF(AND(F5=0,G5=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B5="","",IF(OR($A5="수익",$A5="비용"),"제외 (손익계정)",IF(AND(F5=0,G5=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -13869,11 +14495,11 @@
         <v/>
       </c>
       <c r="B6" s="12">
-        <f>IF(결산명세서!$B6="","",결산명세서!$C6)</f>
+        <f>IF(결산명세서!$B6="","",결산명세서!$D6)</f>
         <v/>
       </c>
       <c r="C6" s="17">
-        <f>IF($B6="","",결산명세서!$H6)</f>
+        <f>IF($B6="","",결산명세서!$I6)</f>
         <v/>
       </c>
       <c r="D6" s="8" t="n">
@@ -13883,15 +14509,15 @@
         <v>48250000</v>
       </c>
       <c r="F6" s="15">
-        <f>IF($B6="","",C6-D6)</f>
+        <f>IF(OR($B6="",$A6="수익",$A6="비용"),"",C6-D6)</f>
         <v/>
       </c>
       <c r="G6" s="15">
-        <f>IF($B6="","",D6-E6)</f>
+        <f>IF(OR($B6="",$A6="수익",$A6="비용"),"",D6-E6)</f>
         <v/>
       </c>
       <c r="H6" s="13">
-        <f>IF($B6="","",IF(AND(F6=0,G6=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B6="","",IF(OR($A6="수익",$A6="비용"),"제외 (손익계정)",IF(AND(F6=0,G6=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -13901,11 +14527,11 @@
         <v/>
       </c>
       <c r="B7" s="12">
-        <f>IF(결산명세서!$B7="","",결산명세서!$C7)</f>
+        <f>IF(결산명세서!$B7="","",결산명세서!$D7)</f>
         <v/>
       </c>
       <c r="C7" s="17">
-        <f>IF($B7="","",결산명세서!$H7)</f>
+        <f>IF($B7="","",결산명세서!$I7)</f>
         <v/>
       </c>
       <c r="D7" s="8" t="n">
@@ -13915,15 +14541,15 @@
         <v>12300000</v>
       </c>
       <c r="F7" s="15">
-        <f>IF($B7="","",C7-D7)</f>
+        <f>IF(OR($B7="",$A7="수익",$A7="비용"),"",C7-D7)</f>
         <v/>
       </c>
       <c r="G7" s="15">
-        <f>IF($B7="","",D7-E7)</f>
+        <f>IF(OR($B7="",$A7="수익",$A7="비용"),"",D7-E7)</f>
         <v/>
       </c>
       <c r="H7" s="13">
-        <f>IF($B7="","",IF(AND(F7=0,G7=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B7="","",IF(OR($A7="수익",$A7="비용"),"제외 (손익계정)",IF(AND(F7=0,G7=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -13933,11 +14559,11 @@
         <v/>
       </c>
       <c r="B8" s="12">
-        <f>IF(결산명세서!$B8="","",결산명세서!$C8)</f>
+        <f>IF(결산명세서!$B8="","",결산명세서!$D8)</f>
         <v/>
       </c>
       <c r="C8" s="17">
-        <f>IF($B8="","",결산명세서!$H8)</f>
+        <f>IF($B8="","",결산명세서!$I8)</f>
         <v/>
       </c>
       <c r="D8" s="8" t="n">
@@ -13947,15 +14573,15 @@
         <v>1800000</v>
       </c>
       <c r="F8" s="15">
-        <f>IF($B8="","",C8-D8)</f>
+        <f>IF(OR($B8="",$A8="수익",$A8="비용"),"",C8-D8)</f>
         <v/>
       </c>
       <c r="G8" s="15">
-        <f>IF($B8="","",D8-E8)</f>
+        <f>IF(OR($B8="",$A8="수익",$A8="비용"),"",D8-E8)</f>
         <v/>
       </c>
       <c r="H8" s="13">
-        <f>IF($B8="","",IF(AND(F8=0,G8=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B8="","",IF(OR($A8="수익",$A8="비용"),"제외 (손익계정)",IF(AND(F8=0,G8=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -13965,11 +14591,11 @@
         <v/>
       </c>
       <c r="B9" s="12">
-        <f>IF(결산명세서!$B9="","",결산명세서!$C9)</f>
+        <f>IF(결산명세서!$B9="","",결산명세서!$D9)</f>
         <v/>
       </c>
       <c r="C9" s="17">
-        <f>IF($B9="","",결산명세서!$H9)</f>
+        <f>IF($B9="","",결산명세서!$I9)</f>
         <v/>
       </c>
       <c r="D9" s="8" t="n">
@@ -13979,15 +14605,15 @@
         <v>700000</v>
       </c>
       <c r="F9" s="15">
-        <f>IF($B9="","",C9-D9)</f>
+        <f>IF(OR($B9="",$A9="수익",$A9="비용"),"",C9-D9)</f>
         <v/>
       </c>
       <c r="G9" s="15">
-        <f>IF($B9="","",D9-E9)</f>
+        <f>IF(OR($B9="",$A9="수익",$A9="비용"),"",D9-E9)</f>
         <v/>
       </c>
       <c r="H9" s="13">
-        <f>IF($B9="","",IF(AND(F9=0,G9=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B9="","",IF(OR($A9="수익",$A9="비용"),"제외 (손익계정)",IF(AND(F9=0,G9=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -13997,11 +14623,11 @@
         <v/>
       </c>
       <c r="B10" s="12">
-        <f>IF(결산명세서!$B10="","",결산명세서!$C10)</f>
+        <f>IF(결산명세서!$B10="","",결산명세서!$D10)</f>
         <v/>
       </c>
       <c r="C10" s="17">
-        <f>IF($B10="","",결산명세서!$H10)</f>
+        <f>IF($B10="","",결산명세서!$I10)</f>
         <v/>
       </c>
       <c r="D10" s="8" t="n">
@@ -14011,15 +14637,15 @@
         <v>23400000</v>
       </c>
       <c r="F10" s="15">
-        <f>IF($B10="","",C10-D10)</f>
+        <f>IF(OR($B10="",$A10="수익",$A10="비용"),"",C10-D10)</f>
         <v/>
       </c>
       <c r="G10" s="15">
-        <f>IF($B10="","",D10-E10)</f>
+        <f>IF(OR($B10="",$A10="수익",$A10="비용"),"",D10-E10)</f>
         <v/>
       </c>
       <c r="H10" s="13">
-        <f>IF($B10="","",IF(AND(F10=0,G10=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B10="","",IF(OR($A10="수익",$A10="비용"),"제외 (손익계정)",IF(AND(F10=0,G10=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -14029,11 +14655,11 @@
         <v/>
       </c>
       <c r="B11" s="12">
-        <f>IF(결산명세서!$B11="","",결산명세서!$C11)</f>
+        <f>IF(결산명세서!$B11="","",결산명세서!$D11)</f>
         <v/>
       </c>
       <c r="C11" s="17">
-        <f>IF($B11="","",결산명세서!$H11)</f>
+        <f>IF($B11="","",결산명세서!$I11)</f>
         <v/>
       </c>
       <c r="D11" s="8" t="n">
@@ -14043,15 +14669,15 @@
         <v>8900000</v>
       </c>
       <c r="F11" s="15">
-        <f>IF($B11="","",C11-D11)</f>
+        <f>IF(OR($B11="",$A11="수익",$A11="비용"),"",C11-D11)</f>
         <v/>
       </c>
       <c r="G11" s="15">
-        <f>IF($B11="","",D11-E11)</f>
+        <f>IF(OR($B11="",$A11="수익",$A11="비용"),"",D11-E11)</f>
         <v/>
       </c>
       <c r="H11" s="13">
-        <f>IF($B11="","",IF(AND(F11=0,G11=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B11="","",IF(OR($A11="수익",$A11="비용"),"제외 (손익계정)",IF(AND(F11=0,G11=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -14061,11 +14687,11 @@
         <v/>
       </c>
       <c r="B12" s="12">
-        <f>IF(결산명세서!$B12="","",결산명세서!$C12)</f>
+        <f>IF(결산명세서!$B12="","",결산명세서!$D12)</f>
         <v/>
       </c>
       <c r="C12" s="17">
-        <f>IF($B12="","",결산명세서!$H12)</f>
+        <f>IF($B12="","",결산명세서!$I12)</f>
         <v/>
       </c>
       <c r="D12" s="8" t="n">
@@ -14075,15 +14701,15 @@
         <v>2450000</v>
       </c>
       <c r="F12" s="15">
-        <f>IF($B12="","",C12-D12)</f>
+        <f>IF(OR($B12="",$A12="수익",$A12="비용"),"",C12-D12)</f>
         <v/>
       </c>
       <c r="G12" s="15">
-        <f>IF($B12="","",D12-E12)</f>
+        <f>IF(OR($B12="",$A12="수익",$A12="비용"),"",D12-E12)</f>
         <v/>
       </c>
       <c r="H12" s="13">
-        <f>IF($B12="","",IF(AND(F12=0,G12=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B12="","",IF(OR($A12="수익",$A12="비용"),"제외 (손익계정)",IF(AND(F12=0,G12=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -14093,11 +14719,11 @@
         <v/>
       </c>
       <c r="B13" s="12">
-        <f>IF(결산명세서!$B13="","",결산명세서!$C13)</f>
+        <f>IF(결산명세서!$B13="","",결산명세서!$D13)</f>
         <v/>
       </c>
       <c r="C13" s="17">
-        <f>IF($B13="","",결산명세서!$H13)</f>
+        <f>IF($B13="","",결산명세서!$I13)</f>
         <v/>
       </c>
       <c r="D13" s="8" t="n">
@@ -14107,15 +14733,15 @@
         <v>1130000</v>
       </c>
       <c r="F13" s="15">
-        <f>IF($B13="","",C13-D13)</f>
+        <f>IF(OR($B13="",$A13="수익",$A13="비용"),"",C13-D13)</f>
         <v/>
       </c>
       <c r="G13" s="15">
-        <f>IF($B13="","",D13-E13)</f>
+        <f>IF(OR($B13="",$A13="수익",$A13="비용"),"",D13-E13)</f>
         <v/>
       </c>
       <c r="H13" s="13">
-        <f>IF($B13="","",IF(AND(F13=0,G13=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B13="","",IF(OR($A13="수익",$A13="비용"),"제외 (손익계정)",IF(AND(F13=0,G13=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -14125,11 +14751,11 @@
         <v/>
       </c>
       <c r="B14" s="12">
-        <f>IF(결산명세서!$B14="","",결산명세서!$C14)</f>
+        <f>IF(결산명세서!$B14="","",결산명세서!$D14)</f>
         <v/>
       </c>
       <c r="C14" s="17">
-        <f>IF($B14="","",결산명세서!$H14)</f>
+        <f>IF($B14="","",결산명세서!$I14)</f>
         <v/>
       </c>
       <c r="D14" s="8" t="n">
@@ -14139,15 +14765,15 @@
         <v>2140000</v>
       </c>
       <c r="F14" s="15">
-        <f>IF($B14="","",C14-D14)</f>
+        <f>IF(OR($B14="",$A14="수익",$A14="비용"),"",C14-D14)</f>
         <v/>
       </c>
       <c r="G14" s="15">
-        <f>IF($B14="","",D14-E14)</f>
+        <f>IF(OR($B14="",$A14="수익",$A14="비용"),"",D14-E14)</f>
         <v/>
       </c>
       <c r="H14" s="13">
-        <f>IF($B14="","",IF(AND(F14=0,G14=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B14="","",IF(OR($A14="수익",$A14="비용"),"제외 (손익계정)",IF(AND(F14=0,G14=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -14157,11 +14783,11 @@
         <v/>
       </c>
       <c r="B15" s="12">
-        <f>IF(결산명세서!$B15="","",결산명세서!$C15)</f>
+        <f>IF(결산명세서!$B15="","",결산명세서!$D15)</f>
         <v/>
       </c>
       <c r="C15" s="17">
-        <f>IF($B15="","",결산명세서!$H15)</f>
+        <f>IF($B15="","",결산명세서!$I15)</f>
         <v/>
       </c>
       <c r="D15" s="8" t="n">
@@ -14171,15 +14797,15 @@
         <v>1500000</v>
       </c>
       <c r="F15" s="15">
-        <f>IF($B15="","",C15-D15)</f>
+        <f>IF(OR($B15="",$A15="수익",$A15="비용"),"",C15-D15)</f>
         <v/>
       </c>
       <c r="G15" s="15">
-        <f>IF($B15="","",D15-E15)</f>
+        <f>IF(OR($B15="",$A15="수익",$A15="비용"),"",D15-E15)</f>
         <v/>
       </c>
       <c r="H15" s="13">
-        <f>IF($B15="","",IF(AND(F15=0,G15=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B15="","",IF(OR($A15="수익",$A15="비용"),"제외 (손익계정)",IF(AND(F15=0,G15=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -14189,11 +14815,11 @@
         <v/>
       </c>
       <c r="B16" s="12">
-        <f>IF(결산명세서!$B16="","",결산명세서!$C16)</f>
+        <f>IF(결산명세서!$B16="","",결산명세서!$D16)</f>
         <v/>
       </c>
       <c r="C16" s="17">
-        <f>IF($B16="","",결산명세서!$H16)</f>
+        <f>IF($B16="","",결산명세서!$I16)</f>
         <v/>
       </c>
       <c r="D16" s="8" t="n">
@@ -14203,15 +14829,15 @@
         <v>20000000</v>
       </c>
       <c r="F16" s="15">
-        <f>IF($B16="","",C16-D16)</f>
+        <f>IF(OR($B16="",$A16="수익",$A16="비용"),"",C16-D16)</f>
         <v/>
       </c>
       <c r="G16" s="15">
-        <f>IF($B16="","",D16-E16)</f>
+        <f>IF(OR($B16="",$A16="수익",$A16="비용"),"",D16-E16)</f>
         <v/>
       </c>
       <c r="H16" s="13">
-        <f>IF($B16="","",IF(AND(F16=0,G16=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B16="","",IF(OR($A16="수익",$A16="비용"),"제외 (손익계정)",IF(AND(F16=0,G16=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -14221,25 +14847,25 @@
         <v/>
       </c>
       <c r="B17" s="12">
-        <f>IF(결산명세서!$B17="","",결산명세서!$C17)</f>
+        <f>IF(결산명세서!$B17="","",결산명세서!$D17)</f>
         <v/>
       </c>
       <c r="C17" s="17">
-        <f>IF($B17="","",결산명세서!$H17)</f>
+        <f>IF($B17="","",결산명세서!$I17)</f>
         <v/>
       </c>
       <c r="D17" s="8" t="n"/>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="15">
-        <f>IF($B17="","",C17-D17)</f>
+        <f>IF(OR($B17="",$A17="수익",$A17="비용"),"",C17-D17)</f>
         <v/>
       </c>
       <c r="G17" s="15">
-        <f>IF($B17="","",D17-E17)</f>
+        <f>IF(OR($B17="",$A17="수익",$A17="비용"),"",D17-E17)</f>
         <v/>
       </c>
       <c r="H17" s="13">
-        <f>IF($B17="","",IF(AND(F17=0,G17=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B17="","",IF(OR($A17="수익",$A17="비용"),"제외 (손익계정)",IF(AND(F17=0,G17=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -14249,25 +14875,25 @@
         <v/>
       </c>
       <c r="B18" s="12">
-        <f>IF(결산명세서!$B18="","",결산명세서!$C18)</f>
+        <f>IF(결산명세서!$B18="","",결산명세서!$D18)</f>
         <v/>
       </c>
       <c r="C18" s="17">
-        <f>IF($B18="","",결산명세서!$H18)</f>
+        <f>IF($B18="","",결산명세서!$I18)</f>
         <v/>
       </c>
       <c r="D18" s="8" t="n"/>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="15">
-        <f>IF($B18="","",C18-D18)</f>
+        <f>IF(OR($B18="",$A18="수익",$A18="비용"),"",C18-D18)</f>
         <v/>
       </c>
       <c r="G18" s="15">
-        <f>IF($B18="","",D18-E18)</f>
+        <f>IF(OR($B18="",$A18="수익",$A18="비용"),"",D18-E18)</f>
         <v/>
       </c>
       <c r="H18" s="13">
-        <f>IF($B18="","",IF(AND(F18=0,G18=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B18="","",IF(OR($A18="수익",$A18="비용"),"제외 (손익계정)",IF(AND(F18=0,G18=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -14277,25 +14903,25 @@
         <v/>
       </c>
       <c r="B19" s="12">
-        <f>IF(결산명세서!$B19="","",결산명세서!$C19)</f>
+        <f>IF(결산명세서!$B19="","",결산명세서!$D19)</f>
         <v/>
       </c>
       <c r="C19" s="17">
-        <f>IF($B19="","",결산명세서!$H19)</f>
+        <f>IF($B19="","",결산명세서!$I19)</f>
         <v/>
       </c>
       <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="15">
-        <f>IF($B19="","",C19-D19)</f>
+        <f>IF(OR($B19="",$A19="수익",$A19="비용"),"",C19-D19)</f>
         <v/>
       </c>
       <c r="G19" s="15">
-        <f>IF($B19="","",D19-E19)</f>
+        <f>IF(OR($B19="",$A19="수익",$A19="비용"),"",D19-E19)</f>
         <v/>
       </c>
       <c r="H19" s="13">
-        <f>IF($B19="","",IF(AND(F19=0,G19=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B19="","",IF(OR($A19="수익",$A19="비용"),"제외 (손익계정)",IF(AND(F19=0,G19=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -14305,25 +14931,25 @@
         <v/>
       </c>
       <c r="B20" s="12">
-        <f>IF(결산명세서!$B20="","",결산명세서!$C20)</f>
+        <f>IF(결산명세서!$B20="","",결산명세서!$D20)</f>
         <v/>
       </c>
       <c r="C20" s="17">
-        <f>IF($B20="","",결산명세서!$H20)</f>
+        <f>IF($B20="","",결산명세서!$I20)</f>
         <v/>
       </c>
       <c r="D20" s="8" t="n"/>
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="15">
-        <f>IF($B20="","",C20-D20)</f>
+        <f>IF(OR($B20="",$A20="수익",$A20="비용"),"",C20-D20)</f>
         <v/>
       </c>
       <c r="G20" s="15">
-        <f>IF($B20="","",D20-E20)</f>
+        <f>IF(OR($B20="",$A20="수익",$A20="비용"),"",D20-E20)</f>
         <v/>
       </c>
       <c r="H20" s="13">
-        <f>IF($B20="","",IF(AND(F20=0,G20=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B20="","",IF(OR($A20="수익",$A20="비용"),"제외 (손익계정)",IF(AND(F20=0,G20=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -14333,25 +14959,25 @@
         <v/>
       </c>
       <c r="B21" s="12">
-        <f>IF(결산명세서!$B21="","",결산명세서!$C21)</f>
+        <f>IF(결산명세서!$B21="","",결산명세서!$D21)</f>
         <v/>
       </c>
       <c r="C21" s="17">
-        <f>IF($B21="","",결산명세서!$H21)</f>
+        <f>IF($B21="","",결산명세서!$I21)</f>
         <v/>
       </c>
       <c r="D21" s="8" t="n"/>
       <c r="E21" s="8" t="n"/>
       <c r="F21" s="15">
-        <f>IF($B21="","",C21-D21)</f>
+        <f>IF(OR($B21="",$A21="수익",$A21="비용"),"",C21-D21)</f>
         <v/>
       </c>
       <c r="G21" s="15">
-        <f>IF($B21="","",D21-E21)</f>
+        <f>IF(OR($B21="",$A21="수익",$A21="비용"),"",D21-E21)</f>
         <v/>
       </c>
       <c r="H21" s="13">
-        <f>IF($B21="","",IF(AND(F21=0,G21=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B21="","",IF(OR($A21="수익",$A21="비용"),"제외 (손익계정)",IF(AND(F21=0,G21=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -14361,25 +14987,25 @@
         <v/>
       </c>
       <c r="B22" s="12">
-        <f>IF(결산명세서!$B22="","",결산명세서!$C22)</f>
+        <f>IF(결산명세서!$B22="","",결산명세서!$D22)</f>
         <v/>
       </c>
       <c r="C22" s="17">
-        <f>IF($B22="","",결산명세서!$H22)</f>
+        <f>IF($B22="","",결산명세서!$I22)</f>
         <v/>
       </c>
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
       <c r="F22" s="15">
-        <f>IF($B22="","",C22-D22)</f>
+        <f>IF(OR($B22="",$A22="수익",$A22="비용"),"",C22-D22)</f>
         <v/>
       </c>
       <c r="G22" s="15">
-        <f>IF($B22="","",D22-E22)</f>
+        <f>IF(OR($B22="",$A22="수익",$A22="비용"),"",D22-E22)</f>
         <v/>
       </c>
       <c r="H22" s="13">
-        <f>IF($B22="","",IF(AND(F22=0,G22=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B22="","",IF(OR($A22="수익",$A22="비용"),"제외 (손익계정)",IF(AND(F22=0,G22=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -14389,25 +15015,25 @@
         <v/>
       </c>
       <c r="B23" s="12">
-        <f>IF(결산명세서!$B23="","",결산명세서!$C23)</f>
+        <f>IF(결산명세서!$B23="","",결산명세서!$D23)</f>
         <v/>
       </c>
       <c r="C23" s="17">
-        <f>IF($B23="","",결산명세서!$H23)</f>
+        <f>IF($B23="","",결산명세서!$I23)</f>
         <v/>
       </c>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="n"/>
       <c r="F23" s="15">
-        <f>IF($B23="","",C23-D23)</f>
+        <f>IF(OR($B23="",$A23="수익",$A23="비용"),"",C23-D23)</f>
         <v/>
       </c>
       <c r="G23" s="15">
-        <f>IF($B23="","",D23-E23)</f>
+        <f>IF(OR($B23="",$A23="수익",$A23="비용"),"",D23-E23)</f>
         <v/>
       </c>
       <c r="H23" s="13">
-        <f>IF($B23="","",IF(AND(F23=0,G23=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B23="","",IF(OR($A23="수익",$A23="비용"),"제외 (손익계정)",IF(AND(F23=0,G23=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -14417,25 +15043,25 @@
         <v/>
       </c>
       <c r="B24" s="12">
-        <f>IF(결산명세서!$B24="","",결산명세서!$C24)</f>
+        <f>IF(결산명세서!$B24="","",결산명세서!$D24)</f>
         <v/>
       </c>
       <c r="C24" s="17">
-        <f>IF($B24="","",결산명세서!$H24)</f>
+        <f>IF($B24="","",결산명세서!$I24)</f>
         <v/>
       </c>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="15">
-        <f>IF($B24="","",C24-D24)</f>
+        <f>IF(OR($B24="",$A24="수익",$A24="비용"),"",C24-D24)</f>
         <v/>
       </c>
       <c r="G24" s="15">
-        <f>IF($B24="","",D24-E24)</f>
+        <f>IF(OR($B24="",$A24="수익",$A24="비용"),"",D24-E24)</f>
         <v/>
       </c>
       <c r="H24" s="13">
-        <f>IF($B24="","",IF(AND(F24=0,G24=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B24="","",IF(OR($A24="수익",$A24="비용"),"제외 (손익계정)",IF(AND(F24=0,G24=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -14445,25 +15071,25 @@
         <v/>
       </c>
       <c r="B25" s="12">
-        <f>IF(결산명세서!$B25="","",결산명세서!$C25)</f>
+        <f>IF(결산명세서!$B25="","",결산명세서!$D25)</f>
         <v/>
       </c>
       <c r="C25" s="17">
-        <f>IF($B25="","",결산명세서!$H25)</f>
+        <f>IF($B25="","",결산명세서!$I25)</f>
         <v/>
       </c>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
       <c r="F25" s="15">
-        <f>IF($B25="","",C25-D25)</f>
+        <f>IF(OR($B25="",$A25="수익",$A25="비용"),"",C25-D25)</f>
         <v/>
       </c>
       <c r="G25" s="15">
-        <f>IF($B25="","",D25-E25)</f>
+        <f>IF(OR($B25="",$A25="수익",$A25="비용"),"",D25-E25)</f>
         <v/>
       </c>
       <c r="H25" s="13">
-        <f>IF($B25="","",IF(AND(F25=0,G25=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B25="","",IF(OR($A25="수익",$A25="비용"),"제외 (손익계정)",IF(AND(F25=0,G25=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -14473,25 +15099,25 @@
         <v/>
       </c>
       <c r="B26" s="12">
-        <f>IF(결산명세서!$B26="","",결산명세서!$C26)</f>
+        <f>IF(결산명세서!$B26="","",결산명세서!$D26)</f>
         <v/>
       </c>
       <c r="C26" s="17">
-        <f>IF($B26="","",결산명세서!$H26)</f>
+        <f>IF($B26="","",결산명세서!$I26)</f>
         <v/>
       </c>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="15">
-        <f>IF($B26="","",C26-D26)</f>
+        <f>IF(OR($B26="",$A26="수익",$A26="비용"),"",C26-D26)</f>
         <v/>
       </c>
       <c r="G26" s="15">
-        <f>IF($B26="","",D26-E26)</f>
+        <f>IF(OR($B26="",$A26="수익",$A26="비용"),"",D26-E26)</f>
         <v/>
       </c>
       <c r="H26" s="13">
-        <f>IF($B26="","",IF(AND(F26=0,G26=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B26="","",IF(OR($A26="수익",$A26="비용"),"제외 (손익계정)",IF(AND(F26=0,G26=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -14501,25 +15127,25 @@
         <v/>
       </c>
       <c r="B27" s="12">
-        <f>IF(결산명세서!$B27="","",결산명세서!$C27)</f>
+        <f>IF(결산명세서!$B27="","",결산명세서!$D27)</f>
         <v/>
       </c>
       <c r="C27" s="17">
-        <f>IF($B27="","",결산명세서!$H27)</f>
+        <f>IF($B27="","",결산명세서!$I27)</f>
         <v/>
       </c>
       <c r="D27" s="8" t="n"/>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="15">
-        <f>IF($B27="","",C27-D27)</f>
+        <f>IF(OR($B27="",$A27="수익",$A27="비용"),"",C27-D27)</f>
         <v/>
       </c>
       <c r="G27" s="15">
-        <f>IF($B27="","",D27-E27)</f>
+        <f>IF(OR($B27="",$A27="수익",$A27="비용"),"",D27-E27)</f>
         <v/>
       </c>
       <c r="H27" s="13">
-        <f>IF($B27="","",IF(AND(F27=0,G27=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B27="","",IF(OR($A27="수익",$A27="비용"),"제외 (손익계정)",IF(AND(F27=0,G27=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -14529,25 +15155,25 @@
         <v/>
       </c>
       <c r="B28" s="12">
-        <f>IF(결산명세서!$B28="","",결산명세서!$C28)</f>
+        <f>IF(결산명세서!$B28="","",결산명세서!$D28)</f>
         <v/>
       </c>
       <c r="C28" s="17">
-        <f>IF($B28="","",결산명세서!$H28)</f>
+        <f>IF($B28="","",결산명세서!$I28)</f>
         <v/>
       </c>
       <c r="D28" s="8" t="n"/>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="15">
-        <f>IF($B28="","",C28-D28)</f>
+        <f>IF(OR($B28="",$A28="수익",$A28="비용"),"",C28-D28)</f>
         <v/>
       </c>
       <c r="G28" s="15">
-        <f>IF($B28="","",D28-E28)</f>
+        <f>IF(OR($B28="",$A28="수익",$A28="비용"),"",D28-E28)</f>
         <v/>
       </c>
       <c r="H28" s="13">
-        <f>IF($B28="","",IF(AND(F28=0,G28=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B28="","",IF(OR($A28="수익",$A28="비용"),"제외 (손익계정)",IF(AND(F28=0,G28=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -14557,25 +15183,25 @@
         <v/>
       </c>
       <c r="B29" s="12">
-        <f>IF(결산명세서!$B29="","",결산명세서!$C29)</f>
+        <f>IF(결산명세서!$B29="","",결산명세서!$D29)</f>
         <v/>
       </c>
       <c r="C29" s="17">
-        <f>IF($B29="","",결산명세서!$H29)</f>
+        <f>IF($B29="","",결산명세서!$I29)</f>
         <v/>
       </c>
       <c r="D29" s="8" t="n"/>
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="15">
-        <f>IF($B29="","",C29-D29)</f>
+        <f>IF(OR($B29="",$A29="수익",$A29="비용"),"",C29-D29)</f>
         <v/>
       </c>
       <c r="G29" s="15">
-        <f>IF($B29="","",D29-E29)</f>
+        <f>IF(OR($B29="",$A29="수익",$A29="비용"),"",D29-E29)</f>
         <v/>
       </c>
       <c r="H29" s="13">
-        <f>IF($B29="","",IF(AND(F29=0,G29=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B29="","",IF(OR($A29="수익",$A29="비용"),"제외 (손익계정)",IF(AND(F29=0,G29=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -14585,25 +15211,25 @@
         <v/>
       </c>
       <c r="B30" s="12">
-        <f>IF(결산명세서!$B30="","",결산명세서!$C30)</f>
+        <f>IF(결산명세서!$B30="","",결산명세서!$D30)</f>
         <v/>
       </c>
       <c r="C30" s="17">
-        <f>IF($B30="","",결산명세서!$H30)</f>
+        <f>IF($B30="","",결산명세서!$I30)</f>
         <v/>
       </c>
       <c r="D30" s="8" t="n"/>
       <c r="E30" s="8" t="n"/>
       <c r="F30" s="15">
-        <f>IF($B30="","",C30-D30)</f>
+        <f>IF(OR($B30="",$A30="수익",$A30="비용"),"",C30-D30)</f>
         <v/>
       </c>
       <c r="G30" s="15">
-        <f>IF($B30="","",D30-E30)</f>
+        <f>IF(OR($B30="",$A30="수익",$A30="비용"),"",D30-E30)</f>
         <v/>
       </c>
       <c r="H30" s="13">
-        <f>IF($B30="","",IF(AND(F30=0,G30=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B30="","",IF(OR($A30="수익",$A30="비용"),"제외 (손익계정)",IF(AND(F30=0,G30=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -14613,25 +15239,25 @@
         <v/>
       </c>
       <c r="B31" s="12">
-        <f>IF(결산명세서!$B31="","",결산명세서!$C31)</f>
+        <f>IF(결산명세서!$B31="","",결산명세서!$D31)</f>
         <v/>
       </c>
       <c r="C31" s="17">
-        <f>IF($B31="","",결산명세서!$H31)</f>
+        <f>IF($B31="","",결산명세서!$I31)</f>
         <v/>
       </c>
       <c r="D31" s="8" t="n"/>
       <c r="E31" s="8" t="n"/>
       <c r="F31" s="15">
-        <f>IF($B31="","",C31-D31)</f>
+        <f>IF(OR($B31="",$A31="수익",$A31="비용"),"",C31-D31)</f>
         <v/>
       </c>
       <c r="G31" s="15">
-        <f>IF($B31="","",D31-E31)</f>
+        <f>IF(OR($B31="",$A31="수익",$A31="비용"),"",D31-E31)</f>
         <v/>
       </c>
       <c r="H31" s="13">
-        <f>IF($B31="","",IF(AND(F31=0,G31=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B31="","",IF(OR($A31="수익",$A31="비용"),"제외 (손익계정)",IF(AND(F31=0,G31=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -14641,25 +15267,25 @@
         <v/>
       </c>
       <c r="B32" s="12">
-        <f>IF(결산명세서!$B32="","",결산명세서!$C32)</f>
+        <f>IF(결산명세서!$B32="","",결산명세서!$D32)</f>
         <v/>
       </c>
       <c r="C32" s="17">
-        <f>IF($B32="","",결산명세서!$H32)</f>
+        <f>IF($B32="","",결산명세서!$I32)</f>
         <v/>
       </c>
       <c r="D32" s="8" t="n"/>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="15">
-        <f>IF($B32="","",C32-D32)</f>
+        <f>IF(OR($B32="",$A32="수익",$A32="비용"),"",C32-D32)</f>
         <v/>
       </c>
       <c r="G32" s="15">
-        <f>IF($B32="","",D32-E32)</f>
+        <f>IF(OR($B32="",$A32="수익",$A32="비용"),"",D32-E32)</f>
         <v/>
       </c>
       <c r="H32" s="13">
-        <f>IF($B32="","",IF(AND(F32=0,G32=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B32="","",IF(OR($A32="수익",$A32="비용"),"제외 (손익계정)",IF(AND(F32=0,G32=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -14669,25 +15295,25 @@
         <v/>
       </c>
       <c r="B33" s="12">
-        <f>IF(결산명세서!$B33="","",결산명세서!$C33)</f>
+        <f>IF(결산명세서!$B33="","",결산명세서!$D33)</f>
         <v/>
       </c>
       <c r="C33" s="17">
-        <f>IF($B33="","",결산명세서!$H33)</f>
+        <f>IF($B33="","",결산명세서!$I33)</f>
         <v/>
       </c>
       <c r="D33" s="8" t="n"/>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="15">
-        <f>IF($B33="","",C33-D33)</f>
+        <f>IF(OR($B33="",$A33="수익",$A33="비용"),"",C33-D33)</f>
         <v/>
       </c>
       <c r="G33" s="15">
-        <f>IF($B33="","",D33-E33)</f>
+        <f>IF(OR($B33="",$A33="수익",$A33="비용"),"",D33-E33)</f>
         <v/>
       </c>
       <c r="H33" s="13">
-        <f>IF($B33="","",IF(AND(F33=0,G33=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B33="","",IF(OR($A33="수익",$A33="비용"),"제외 (손익계정)",IF(AND(F33=0,G33=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -14697,25 +15323,25 @@
         <v/>
       </c>
       <c r="B34" s="12">
-        <f>IF(결산명세서!$B34="","",결산명세서!$C34)</f>
+        <f>IF(결산명세서!$B34="","",결산명세서!$D34)</f>
         <v/>
       </c>
       <c r="C34" s="17">
-        <f>IF($B34="","",결산명세서!$H34)</f>
+        <f>IF($B34="","",결산명세서!$I34)</f>
         <v/>
       </c>
       <c r="D34" s="8" t="n"/>
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="15">
-        <f>IF($B34="","",C34-D34)</f>
+        <f>IF(OR($B34="",$A34="수익",$A34="비용"),"",C34-D34)</f>
         <v/>
       </c>
       <c r="G34" s="15">
-        <f>IF($B34="","",D34-E34)</f>
+        <f>IF(OR($B34="",$A34="수익",$A34="비용"),"",D34-E34)</f>
         <v/>
       </c>
       <c r="H34" s="13">
-        <f>IF($B34="","",IF(AND(F34=0,G34=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B34="","",IF(OR($A34="수익",$A34="비용"),"제외 (손익계정)",IF(AND(F34=0,G34=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -14725,25 +15351,25 @@
         <v/>
       </c>
       <c r="B35" s="12">
-        <f>IF(결산명세서!$B35="","",결산명세서!$C35)</f>
+        <f>IF(결산명세서!$B35="","",결산명세서!$D35)</f>
         <v/>
       </c>
       <c r="C35" s="17">
-        <f>IF($B35="","",결산명세서!$H35)</f>
+        <f>IF($B35="","",결산명세서!$I35)</f>
         <v/>
       </c>
       <c r="D35" s="8" t="n"/>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="15">
-        <f>IF($B35="","",C35-D35)</f>
+        <f>IF(OR($B35="",$A35="수익",$A35="비용"),"",C35-D35)</f>
         <v/>
       </c>
       <c r="G35" s="15">
-        <f>IF($B35="","",D35-E35)</f>
+        <f>IF(OR($B35="",$A35="수익",$A35="비용"),"",D35-E35)</f>
         <v/>
       </c>
       <c r="H35" s="13">
-        <f>IF($B35="","",IF(AND(F35=0,G35=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B35="","",IF(OR($A35="수익",$A35="비용"),"제외 (손익계정)",IF(AND(F35=0,G35=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -14753,25 +15379,25 @@
         <v/>
       </c>
       <c r="B36" s="12">
-        <f>IF(결산명세서!$B36="","",결산명세서!$C36)</f>
+        <f>IF(결산명세서!$B36="","",결산명세서!$D36)</f>
         <v/>
       </c>
       <c r="C36" s="17">
-        <f>IF($B36="","",결산명세서!$H36)</f>
+        <f>IF($B36="","",결산명세서!$I36)</f>
         <v/>
       </c>
       <c r="D36" s="8" t="n"/>
       <c r="E36" s="8" t="n"/>
       <c r="F36" s="15">
-        <f>IF($B36="","",C36-D36)</f>
+        <f>IF(OR($B36="",$A36="수익",$A36="비용"),"",C36-D36)</f>
         <v/>
       </c>
       <c r="G36" s="15">
-        <f>IF($B36="","",D36-E36)</f>
+        <f>IF(OR($B36="",$A36="수익",$A36="비용"),"",D36-E36)</f>
         <v/>
       </c>
       <c r="H36" s="13">
-        <f>IF($B36="","",IF(AND(F36=0,G36=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B36="","",IF(OR($A36="수익",$A36="비용"),"제외 (손익계정)",IF(AND(F36=0,G36=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -14781,25 +15407,25 @@
         <v/>
       </c>
       <c r="B37" s="12">
-        <f>IF(결산명세서!$B37="","",결산명세서!$C37)</f>
+        <f>IF(결산명세서!$B37="","",결산명세서!$D37)</f>
         <v/>
       </c>
       <c r="C37" s="17">
-        <f>IF($B37="","",결산명세서!$H37)</f>
+        <f>IF($B37="","",결산명세서!$I37)</f>
         <v/>
       </c>
       <c r="D37" s="8" t="n"/>
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="15">
-        <f>IF($B37="","",C37-D37)</f>
+        <f>IF(OR($B37="",$A37="수익",$A37="비용"),"",C37-D37)</f>
         <v/>
       </c>
       <c r="G37" s="15">
-        <f>IF($B37="","",D37-E37)</f>
+        <f>IF(OR($B37="",$A37="수익",$A37="비용"),"",D37-E37)</f>
         <v/>
       </c>
       <c r="H37" s="13">
-        <f>IF($B37="","",IF(AND(F37=0,G37=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B37="","",IF(OR($A37="수익",$A37="비용"),"제외 (손익계정)",IF(AND(F37=0,G37=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -14809,25 +15435,25 @@
         <v/>
       </c>
       <c r="B38" s="12">
-        <f>IF(결산명세서!$B38="","",결산명세서!$C38)</f>
+        <f>IF(결산명세서!$B38="","",결산명세서!$D38)</f>
         <v/>
       </c>
       <c r="C38" s="17">
-        <f>IF($B38="","",결산명세서!$H38)</f>
+        <f>IF($B38="","",결산명세서!$I38)</f>
         <v/>
       </c>
       <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="15">
-        <f>IF($B38="","",C38-D38)</f>
+        <f>IF(OR($B38="",$A38="수익",$A38="비용"),"",C38-D38)</f>
         <v/>
       </c>
       <c r="G38" s="15">
-        <f>IF($B38="","",D38-E38)</f>
+        <f>IF(OR($B38="",$A38="수익",$A38="비용"),"",D38-E38)</f>
         <v/>
       </c>
       <c r="H38" s="13">
-        <f>IF($B38="","",IF(AND(F38=0,G38=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B38="","",IF(OR($A38="수익",$A38="비용"),"제외 (손익계정)",IF(AND(F38=0,G38=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -14837,25 +15463,25 @@
         <v/>
       </c>
       <c r="B39" s="12">
-        <f>IF(결산명세서!$B39="","",결산명세서!$C39)</f>
+        <f>IF(결산명세서!$B39="","",결산명세서!$D39)</f>
         <v/>
       </c>
       <c r="C39" s="17">
-        <f>IF($B39="","",결산명세서!$H39)</f>
+        <f>IF($B39="","",결산명세서!$I39)</f>
         <v/>
       </c>
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="n"/>
       <c r="F39" s="15">
-        <f>IF($B39="","",C39-D39)</f>
+        <f>IF(OR($B39="",$A39="수익",$A39="비용"),"",C39-D39)</f>
         <v/>
       </c>
       <c r="G39" s="15">
-        <f>IF($B39="","",D39-E39)</f>
+        <f>IF(OR($B39="",$A39="수익",$A39="비용"),"",D39-E39)</f>
         <v/>
       </c>
       <c r="H39" s="13">
-        <f>IF($B39="","",IF(AND(F39=0,G39=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B39="","",IF(OR($A39="수익",$A39="비용"),"제외 (손익계정)",IF(AND(F39=0,G39=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -14865,25 +15491,25 @@
         <v/>
       </c>
       <c r="B40" s="12">
-        <f>IF(결산명세서!$B40="","",결산명세서!$C40)</f>
+        <f>IF(결산명세서!$B40="","",결산명세서!$D40)</f>
         <v/>
       </c>
       <c r="C40" s="17">
-        <f>IF($B40="","",결산명세서!$H40)</f>
+        <f>IF($B40="","",결산명세서!$I40)</f>
         <v/>
       </c>
       <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="15">
-        <f>IF($B40="","",C40-D40)</f>
+        <f>IF(OR($B40="",$A40="수익",$A40="비용"),"",C40-D40)</f>
         <v/>
       </c>
       <c r="G40" s="15">
-        <f>IF($B40="","",D40-E40)</f>
+        <f>IF(OR($B40="",$A40="수익",$A40="비용"),"",D40-E40)</f>
         <v/>
       </c>
       <c r="H40" s="13">
-        <f>IF($B40="","",IF(AND(F40=0,G40=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B40="","",IF(OR($A40="수익",$A40="비용"),"제외 (손익계정)",IF(AND(F40=0,G40=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -14893,25 +15519,25 @@
         <v/>
       </c>
       <c r="B41" s="12">
-        <f>IF(결산명세서!$B41="","",결산명세서!$C41)</f>
+        <f>IF(결산명세서!$B41="","",결산명세서!$D41)</f>
         <v/>
       </c>
       <c r="C41" s="17">
-        <f>IF($B41="","",결산명세서!$H41)</f>
+        <f>IF($B41="","",결산명세서!$I41)</f>
         <v/>
       </c>
       <c r="D41" s="8" t="n"/>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="15">
-        <f>IF($B41="","",C41-D41)</f>
+        <f>IF(OR($B41="",$A41="수익",$A41="비용"),"",C41-D41)</f>
         <v/>
       </c>
       <c r="G41" s="15">
-        <f>IF($B41="","",D41-E41)</f>
+        <f>IF(OR($B41="",$A41="수익",$A41="비용"),"",D41-E41)</f>
         <v/>
       </c>
       <c r="H41" s="13">
-        <f>IF($B41="","",IF(AND(F41=0,G41=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B41="","",IF(OR($A41="수익",$A41="비용"),"제외 (손익계정)",IF(AND(F41=0,G41=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -14921,25 +15547,25 @@
         <v/>
       </c>
       <c r="B42" s="12">
-        <f>IF(결산명세서!$B42="","",결산명세서!$C42)</f>
+        <f>IF(결산명세서!$B42="","",결산명세서!$D42)</f>
         <v/>
       </c>
       <c r="C42" s="17">
-        <f>IF($B42="","",결산명세서!$H42)</f>
+        <f>IF($B42="","",결산명세서!$I42)</f>
         <v/>
       </c>
       <c r="D42" s="8" t="n"/>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="15">
-        <f>IF($B42="","",C42-D42)</f>
+        <f>IF(OR($B42="",$A42="수익",$A42="비용"),"",C42-D42)</f>
         <v/>
       </c>
       <c r="G42" s="15">
-        <f>IF($B42="","",D42-E42)</f>
+        <f>IF(OR($B42="",$A42="수익",$A42="비용"),"",D42-E42)</f>
         <v/>
       </c>
       <c r="H42" s="13">
-        <f>IF($B42="","",IF(AND(F42=0,G42=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B42="","",IF(OR($A42="수익",$A42="비용"),"제외 (손익계정)",IF(AND(F42=0,G42=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -14949,25 +15575,25 @@
         <v/>
       </c>
       <c r="B43" s="12">
-        <f>IF(결산명세서!$B43="","",결산명세서!$C43)</f>
+        <f>IF(결산명세서!$B43="","",결산명세서!$D43)</f>
         <v/>
       </c>
       <c r="C43" s="17">
-        <f>IF($B43="","",결산명세서!$H43)</f>
+        <f>IF($B43="","",결산명세서!$I43)</f>
         <v/>
       </c>
       <c r="D43" s="8" t="n"/>
       <c r="E43" s="8" t="n"/>
       <c r="F43" s="15">
-        <f>IF($B43="","",C43-D43)</f>
+        <f>IF(OR($B43="",$A43="수익",$A43="비용"),"",C43-D43)</f>
         <v/>
       </c>
       <c r="G43" s="15">
-        <f>IF($B43="","",D43-E43)</f>
+        <f>IF(OR($B43="",$A43="수익",$A43="비용"),"",D43-E43)</f>
         <v/>
       </c>
       <c r="H43" s="13">
-        <f>IF($B43="","",IF(AND(F43=0,G43=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B43="","",IF(OR($A43="수익",$A43="비용"),"제외 (손익계정)",IF(AND(F43=0,G43=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -14977,25 +15603,25 @@
         <v/>
       </c>
       <c r="B44" s="12">
-        <f>IF(결산명세서!$B44="","",결산명세서!$C44)</f>
+        <f>IF(결산명세서!$B44="","",결산명세서!$D44)</f>
         <v/>
       </c>
       <c r="C44" s="17">
-        <f>IF($B44="","",결산명세서!$H44)</f>
+        <f>IF($B44="","",결산명세서!$I44)</f>
         <v/>
       </c>
       <c r="D44" s="8" t="n"/>
       <c r="E44" s="8" t="n"/>
       <c r="F44" s="15">
-        <f>IF($B44="","",C44-D44)</f>
+        <f>IF(OR($B44="",$A44="수익",$A44="비용"),"",C44-D44)</f>
         <v/>
       </c>
       <c r="G44" s="15">
-        <f>IF($B44="","",D44-E44)</f>
+        <f>IF(OR($B44="",$A44="수익",$A44="비용"),"",D44-E44)</f>
         <v/>
       </c>
       <c r="H44" s="13">
-        <f>IF($B44="","",IF(AND(F44=0,G44=0),"✔ 일치","✖ 확인 필요"))</f>
+        <f>IF($B44="","",IF(OR($A44="수익",$A44="비용"),"제외 (손익계정)",IF(AND(F44=0,G44=0),"✔ 일치","✖ 확인 필요")))</f>
         <v/>
       </c>
     </row>
@@ -15063,7 +15689,7 @@
         <v/>
       </c>
       <c r="B5" s="3">
-        <f>IF($F5="","",INDEX(결산명세서!$C$5:$C$44,1))</f>
+        <f>IF($F5="","",INDEX(결산명세서!$D$5:$D$44,1))</f>
         <v/>
       </c>
       <c r="D5" s="3">
@@ -15071,7 +15697,7 @@
         <v/>
       </c>
       <c r="E5" s="22">
-        <f>IF($F5="","",INDEX(결산명세서!$H$5:$H$44,1))</f>
+        <f>IF($F5="","",INDEX(결산명세서!$I$5:$I$44,1))</f>
         <v/>
       </c>
       <c r="F5" s="23">
@@ -15437,11 +16063,11 @@
         <v/>
       </c>
       <c r="D22" s="15">
-        <f>IF($F5="","",INDEX(결산명세서!$D$5:$D$44,1))</f>
+        <f>IF($F5="","",INDEX(결산명세서!$E$5:$E$44,1))</f>
         <v/>
       </c>
       <c r="E22" s="15">
-        <f>IF($F5="","",INDEX(결산명세서!$E$5:$E$44,1))</f>
+        <f>IF($F5="","",INDEX(결산명세서!$F$5:$F$44,1))</f>
         <v/>
       </c>
     </row>
@@ -15451,11 +16077,11 @@
         <v/>
       </c>
       <c r="D23" s="15">
-        <f>IF($F5="","",INDEX(결산명세서!$F$5:$F$44,1))</f>
+        <f>IF($F5="","",INDEX(결산명세서!$G$5:$G$44,1))</f>
         <v/>
       </c>
       <c r="E23" s="15">
-        <f>IF($F5="","",INDEX(결산명세서!$G$5:$G$44,1))</f>
+        <f>IF($F5="","",INDEX(결산명세서!$H$5:$H$44,1))</f>
         <v/>
       </c>
     </row>
@@ -15476,7 +16102,7 @@
         <v/>
       </c>
       <c r="B26" s="3">
-        <f>IF($F26="","",INDEX(결산명세서!$C$5:$C$44,2))</f>
+        <f>IF($F26="","",INDEX(결산명세서!$D$5:$D$44,2))</f>
         <v/>
       </c>
       <c r="D26" s="3">
@@ -15484,7 +16110,7 @@
         <v/>
       </c>
       <c r="E26" s="22">
-        <f>IF($F26="","",INDEX(결산명세서!$H$5:$H$44,2))</f>
+        <f>IF($F26="","",INDEX(결산명세서!$I$5:$I$44,2))</f>
         <v/>
       </c>
       <c r="F26" s="23">
@@ -15850,11 +16476,11 @@
         <v/>
       </c>
       <c r="D43" s="15">
-        <f>IF($F26="","",INDEX(결산명세서!$D$5:$D$44,2))</f>
+        <f>IF($F26="","",INDEX(결산명세서!$E$5:$E$44,2))</f>
         <v/>
       </c>
       <c r="E43" s="15">
-        <f>IF($F26="","",INDEX(결산명세서!$E$5:$E$44,2))</f>
+        <f>IF($F26="","",INDEX(결산명세서!$F$5:$F$44,2))</f>
         <v/>
       </c>
     </row>
@@ -15864,11 +16490,11 @@
         <v/>
       </c>
       <c r="D44" s="15">
-        <f>IF($F26="","",INDEX(결산명세서!$F$5:$F$44,2))</f>
+        <f>IF($F26="","",INDEX(결산명세서!$G$5:$G$44,2))</f>
         <v/>
       </c>
       <c r="E44" s="15">
-        <f>IF($F26="","",INDEX(결산명세서!$G$5:$G$44,2))</f>
+        <f>IF($F26="","",INDEX(결산명세서!$H$5:$H$44,2))</f>
         <v/>
       </c>
     </row>
@@ -15889,7 +16515,7 @@
         <v/>
       </c>
       <c r="B47" s="3">
-        <f>IF($F47="","",INDEX(결산명세서!$C$5:$C$44,3))</f>
+        <f>IF($F47="","",INDEX(결산명세서!$D$5:$D$44,3))</f>
         <v/>
       </c>
       <c r="D47" s="3">
@@ -15897,7 +16523,7 @@
         <v/>
       </c>
       <c r="E47" s="22">
-        <f>IF($F47="","",INDEX(결산명세서!$H$5:$H$44,3))</f>
+        <f>IF($F47="","",INDEX(결산명세서!$I$5:$I$44,3))</f>
         <v/>
       </c>
       <c r="F47" s="23">
@@ -16263,11 +16889,11 @@
         <v/>
       </c>
       <c r="D64" s="15">
-        <f>IF($F47="","",INDEX(결산명세서!$D$5:$D$44,3))</f>
+        <f>IF($F47="","",INDEX(결산명세서!$E$5:$E$44,3))</f>
         <v/>
       </c>
       <c r="E64" s="15">
-        <f>IF($F47="","",INDEX(결산명세서!$E$5:$E$44,3))</f>
+        <f>IF($F47="","",INDEX(결산명세서!$F$5:$F$44,3))</f>
         <v/>
       </c>
     </row>
@@ -16277,11 +16903,11 @@
         <v/>
       </c>
       <c r="D65" s="15">
-        <f>IF($F47="","",INDEX(결산명세서!$F$5:$F$44,3))</f>
+        <f>IF($F47="","",INDEX(결산명세서!$G$5:$G$44,3))</f>
         <v/>
       </c>
       <c r="E65" s="15">
-        <f>IF($F47="","",INDEX(결산명세서!$G$5:$G$44,3))</f>
+        <f>IF($F47="","",INDEX(결산명세서!$H$5:$H$44,3))</f>
         <v/>
       </c>
     </row>
@@ -16302,7 +16928,7 @@
         <v/>
       </c>
       <c r="B68" s="3">
-        <f>IF($F68="","",INDEX(결산명세서!$C$5:$C$44,4))</f>
+        <f>IF($F68="","",INDEX(결산명세서!$D$5:$D$44,4))</f>
         <v/>
       </c>
       <c r="D68" s="3">
@@ -16310,7 +16936,7 @@
         <v/>
       </c>
       <c r="E68" s="22">
-        <f>IF($F68="","",INDEX(결산명세서!$H$5:$H$44,4))</f>
+        <f>IF($F68="","",INDEX(결산명세서!$I$5:$I$44,4))</f>
         <v/>
       </c>
       <c r="F68" s="23">
@@ -16676,11 +17302,11 @@
         <v/>
       </c>
       <c r="D85" s="15">
-        <f>IF($F68="","",INDEX(결산명세서!$D$5:$D$44,4))</f>
+        <f>IF($F68="","",INDEX(결산명세서!$E$5:$E$44,4))</f>
         <v/>
       </c>
       <c r="E85" s="15">
-        <f>IF($F68="","",INDEX(결산명세서!$E$5:$E$44,4))</f>
+        <f>IF($F68="","",INDEX(결산명세서!$F$5:$F$44,4))</f>
         <v/>
       </c>
     </row>
@@ -16690,11 +17316,11 @@
         <v/>
       </c>
       <c r="D86" s="15">
-        <f>IF($F68="","",INDEX(결산명세서!$F$5:$F$44,4))</f>
+        <f>IF($F68="","",INDEX(결산명세서!$G$5:$G$44,4))</f>
         <v/>
       </c>
       <c r="E86" s="15">
-        <f>IF($F68="","",INDEX(결산명세서!$G$5:$G$44,4))</f>
+        <f>IF($F68="","",INDEX(결산명세서!$H$5:$H$44,4))</f>
         <v/>
       </c>
     </row>
@@ -16715,7 +17341,7 @@
         <v/>
       </c>
       <c r="B89" s="3">
-        <f>IF($F89="","",INDEX(결산명세서!$C$5:$C$44,5))</f>
+        <f>IF($F89="","",INDEX(결산명세서!$D$5:$D$44,5))</f>
         <v/>
       </c>
       <c r="D89" s="3">
@@ -16723,7 +17349,7 @@
         <v/>
       </c>
       <c r="E89" s="22">
-        <f>IF($F89="","",INDEX(결산명세서!$H$5:$H$44,5))</f>
+        <f>IF($F89="","",INDEX(결산명세서!$I$5:$I$44,5))</f>
         <v/>
       </c>
       <c r="F89" s="23">
@@ -17089,11 +17715,11 @@
         <v/>
       </c>
       <c r="D106" s="15">
-        <f>IF($F89="","",INDEX(결산명세서!$D$5:$D$44,5))</f>
+        <f>IF($F89="","",INDEX(결산명세서!$E$5:$E$44,5))</f>
         <v/>
       </c>
       <c r="E106" s="15">
-        <f>IF($F89="","",INDEX(결산명세서!$E$5:$E$44,5))</f>
+        <f>IF($F89="","",INDEX(결산명세서!$F$5:$F$44,5))</f>
         <v/>
       </c>
     </row>
@@ -17103,11 +17729,11 @@
         <v/>
       </c>
       <c r="D107" s="15">
-        <f>IF($F89="","",INDEX(결산명세서!$F$5:$F$44,5))</f>
+        <f>IF($F89="","",INDEX(결산명세서!$G$5:$G$44,5))</f>
         <v/>
       </c>
       <c r="E107" s="15">
-        <f>IF($F89="","",INDEX(결산명세서!$G$5:$G$44,5))</f>
+        <f>IF($F89="","",INDEX(결산명세서!$H$5:$H$44,5))</f>
         <v/>
       </c>
     </row>
@@ -17128,7 +17754,7 @@
         <v/>
       </c>
       <c r="B110" s="3">
-        <f>IF($F110="","",INDEX(결산명세서!$C$5:$C$44,6))</f>
+        <f>IF($F110="","",INDEX(결산명세서!$D$5:$D$44,6))</f>
         <v/>
       </c>
       <c r="D110" s="3">
@@ -17136,7 +17762,7 @@
         <v/>
       </c>
       <c r="E110" s="22">
-        <f>IF($F110="","",INDEX(결산명세서!$H$5:$H$44,6))</f>
+        <f>IF($F110="","",INDEX(결산명세서!$I$5:$I$44,6))</f>
         <v/>
       </c>
       <c r="F110" s="23">
@@ -17502,11 +18128,11 @@
         <v/>
       </c>
       <c r="D127" s="15">
-        <f>IF($F110="","",INDEX(결산명세서!$D$5:$D$44,6))</f>
+        <f>IF($F110="","",INDEX(결산명세서!$E$5:$E$44,6))</f>
         <v/>
       </c>
       <c r="E127" s="15">
-        <f>IF($F110="","",INDEX(결산명세서!$E$5:$E$44,6))</f>
+        <f>IF($F110="","",INDEX(결산명세서!$F$5:$F$44,6))</f>
         <v/>
       </c>
     </row>
@@ -17516,11 +18142,11 @@
         <v/>
       </c>
       <c r="D128" s="15">
-        <f>IF($F110="","",INDEX(결산명세서!$F$5:$F$44,6))</f>
+        <f>IF($F110="","",INDEX(결산명세서!$G$5:$G$44,6))</f>
         <v/>
       </c>
       <c r="E128" s="15">
-        <f>IF($F110="","",INDEX(결산명세서!$G$5:$G$44,6))</f>
+        <f>IF($F110="","",INDEX(결산명세서!$H$5:$H$44,6))</f>
         <v/>
       </c>
     </row>
@@ -17541,7 +18167,7 @@
         <v/>
       </c>
       <c r="B131" s="3">
-        <f>IF($F131="","",INDEX(결산명세서!$C$5:$C$44,7))</f>
+        <f>IF($F131="","",INDEX(결산명세서!$D$5:$D$44,7))</f>
         <v/>
       </c>
       <c r="D131" s="3">
@@ -17549,7 +18175,7 @@
         <v/>
       </c>
       <c r="E131" s="22">
-        <f>IF($F131="","",INDEX(결산명세서!$H$5:$H$44,7))</f>
+        <f>IF($F131="","",INDEX(결산명세서!$I$5:$I$44,7))</f>
         <v/>
       </c>
       <c r="F131" s="23">
@@ -17915,11 +18541,11 @@
         <v/>
       </c>
       <c r="D148" s="15">
-        <f>IF($F131="","",INDEX(결산명세서!$D$5:$D$44,7))</f>
+        <f>IF($F131="","",INDEX(결산명세서!$E$5:$E$44,7))</f>
         <v/>
       </c>
       <c r="E148" s="15">
-        <f>IF($F131="","",INDEX(결산명세서!$E$5:$E$44,7))</f>
+        <f>IF($F131="","",INDEX(결산명세서!$F$5:$F$44,7))</f>
         <v/>
       </c>
     </row>
@@ -17929,11 +18555,11 @@
         <v/>
       </c>
       <c r="D149" s="15">
-        <f>IF($F131="","",INDEX(결산명세서!$F$5:$F$44,7))</f>
+        <f>IF($F131="","",INDEX(결산명세서!$G$5:$G$44,7))</f>
         <v/>
       </c>
       <c r="E149" s="15">
-        <f>IF($F131="","",INDEX(결산명세서!$G$5:$G$44,7))</f>
+        <f>IF($F131="","",INDEX(결산명세서!$H$5:$H$44,7))</f>
         <v/>
       </c>
     </row>
@@ -17954,7 +18580,7 @@
         <v/>
       </c>
       <c r="B152" s="3">
-        <f>IF($F152="","",INDEX(결산명세서!$C$5:$C$44,8))</f>
+        <f>IF($F152="","",INDEX(결산명세서!$D$5:$D$44,8))</f>
         <v/>
       </c>
       <c r="D152" s="3">
@@ -17962,7 +18588,7 @@
         <v/>
       </c>
       <c r="E152" s="22">
-        <f>IF($F152="","",INDEX(결산명세서!$H$5:$H$44,8))</f>
+        <f>IF($F152="","",INDEX(결산명세서!$I$5:$I$44,8))</f>
         <v/>
       </c>
       <c r="F152" s="23">
@@ -18328,11 +18954,11 @@
         <v/>
       </c>
       <c r="D169" s="15">
-        <f>IF($F152="","",INDEX(결산명세서!$D$5:$D$44,8))</f>
+        <f>IF($F152="","",INDEX(결산명세서!$E$5:$E$44,8))</f>
         <v/>
       </c>
       <c r="E169" s="15">
-        <f>IF($F152="","",INDEX(결산명세서!$E$5:$E$44,8))</f>
+        <f>IF($F152="","",INDEX(결산명세서!$F$5:$F$44,8))</f>
         <v/>
       </c>
     </row>
@@ -18342,11 +18968,11 @@
         <v/>
       </c>
       <c r="D170" s="15">
-        <f>IF($F152="","",INDEX(결산명세서!$F$5:$F$44,8))</f>
+        <f>IF($F152="","",INDEX(결산명세서!$G$5:$G$44,8))</f>
         <v/>
       </c>
       <c r="E170" s="15">
-        <f>IF($F152="","",INDEX(결산명세서!$G$5:$G$44,8))</f>
+        <f>IF($F152="","",INDEX(결산명세서!$H$5:$H$44,8))</f>
         <v/>
       </c>
     </row>
@@ -18367,7 +18993,7 @@
         <v/>
       </c>
       <c r="B173" s="3">
-        <f>IF($F173="","",INDEX(결산명세서!$C$5:$C$44,9))</f>
+        <f>IF($F173="","",INDEX(결산명세서!$D$5:$D$44,9))</f>
         <v/>
       </c>
       <c r="D173" s="3">
@@ -18375,7 +19001,7 @@
         <v/>
       </c>
       <c r="E173" s="22">
-        <f>IF($F173="","",INDEX(결산명세서!$H$5:$H$44,9))</f>
+        <f>IF($F173="","",INDEX(결산명세서!$I$5:$I$44,9))</f>
         <v/>
       </c>
       <c r="F173" s="23">
@@ -18741,11 +19367,11 @@
         <v/>
       </c>
       <c r="D190" s="15">
-        <f>IF($F173="","",INDEX(결산명세서!$D$5:$D$44,9))</f>
+        <f>IF($F173="","",INDEX(결산명세서!$E$5:$E$44,9))</f>
         <v/>
       </c>
       <c r="E190" s="15">
-        <f>IF($F173="","",INDEX(결산명세서!$E$5:$E$44,9))</f>
+        <f>IF($F173="","",INDEX(결산명세서!$F$5:$F$44,9))</f>
         <v/>
       </c>
     </row>
@@ -18755,11 +19381,11 @@
         <v/>
       </c>
       <c r="D191" s="15">
-        <f>IF($F173="","",INDEX(결산명세서!$F$5:$F$44,9))</f>
+        <f>IF($F173="","",INDEX(결산명세서!$G$5:$G$44,9))</f>
         <v/>
       </c>
       <c r="E191" s="15">
-        <f>IF($F173="","",INDEX(결산명세서!$G$5:$G$44,9))</f>
+        <f>IF($F173="","",INDEX(결산명세서!$H$5:$H$44,9))</f>
         <v/>
       </c>
     </row>
@@ -18780,7 +19406,7 @@
         <v/>
       </c>
       <c r="B194" s="3">
-        <f>IF($F194="","",INDEX(결산명세서!$C$5:$C$44,10))</f>
+        <f>IF($F194="","",INDEX(결산명세서!$D$5:$D$44,10))</f>
         <v/>
       </c>
       <c r="D194" s="3">
@@ -18788,7 +19414,7 @@
         <v/>
       </c>
       <c r="E194" s="22">
-        <f>IF($F194="","",INDEX(결산명세서!$H$5:$H$44,10))</f>
+        <f>IF($F194="","",INDEX(결산명세서!$I$5:$I$44,10))</f>
         <v/>
       </c>
       <c r="F194" s="23">
@@ -19154,11 +19780,11 @@
         <v/>
       </c>
       <c r="D211" s="15">
-        <f>IF($F194="","",INDEX(결산명세서!$D$5:$D$44,10))</f>
+        <f>IF($F194="","",INDEX(결산명세서!$E$5:$E$44,10))</f>
         <v/>
       </c>
       <c r="E211" s="15">
-        <f>IF($F194="","",INDEX(결산명세서!$E$5:$E$44,10))</f>
+        <f>IF($F194="","",INDEX(결산명세서!$F$5:$F$44,10))</f>
         <v/>
       </c>
     </row>
@@ -19168,11 +19794,11 @@
         <v/>
       </c>
       <c r="D212" s="15">
-        <f>IF($F194="","",INDEX(결산명세서!$F$5:$F$44,10))</f>
+        <f>IF($F194="","",INDEX(결산명세서!$G$5:$G$44,10))</f>
         <v/>
       </c>
       <c r="E212" s="15">
-        <f>IF($F194="","",INDEX(결산명세서!$G$5:$G$44,10))</f>
+        <f>IF($F194="","",INDEX(결산명세서!$H$5:$H$44,10))</f>
         <v/>
       </c>
     </row>
@@ -19193,7 +19819,7 @@
         <v/>
       </c>
       <c r="B215" s="3">
-        <f>IF($F215="","",INDEX(결산명세서!$C$5:$C$44,11))</f>
+        <f>IF($F215="","",INDEX(결산명세서!$D$5:$D$44,11))</f>
         <v/>
       </c>
       <c r="D215" s="3">
@@ -19201,7 +19827,7 @@
         <v/>
       </c>
       <c r="E215" s="22">
-        <f>IF($F215="","",INDEX(결산명세서!$H$5:$H$44,11))</f>
+        <f>IF($F215="","",INDEX(결산명세서!$I$5:$I$44,11))</f>
         <v/>
       </c>
       <c r="F215" s="23">
@@ -19567,11 +20193,11 @@
         <v/>
       </c>
       <c r="D232" s="15">
-        <f>IF($F215="","",INDEX(결산명세서!$D$5:$D$44,11))</f>
+        <f>IF($F215="","",INDEX(결산명세서!$E$5:$E$44,11))</f>
         <v/>
       </c>
       <c r="E232" s="15">
-        <f>IF($F215="","",INDEX(결산명세서!$E$5:$E$44,11))</f>
+        <f>IF($F215="","",INDEX(결산명세서!$F$5:$F$44,11))</f>
         <v/>
       </c>
     </row>
@@ -19581,11 +20207,11 @@
         <v/>
       </c>
       <c r="D233" s="15">
-        <f>IF($F215="","",INDEX(결산명세서!$F$5:$F$44,11))</f>
+        <f>IF($F215="","",INDEX(결산명세서!$G$5:$G$44,11))</f>
         <v/>
       </c>
       <c r="E233" s="15">
-        <f>IF($F215="","",INDEX(결산명세서!$G$5:$G$44,11))</f>
+        <f>IF($F215="","",INDEX(결산명세서!$H$5:$H$44,11))</f>
         <v/>
       </c>
     </row>
@@ -19606,7 +20232,7 @@
         <v/>
       </c>
       <c r="B236" s="3">
-        <f>IF($F236="","",INDEX(결산명세서!$C$5:$C$44,12))</f>
+        <f>IF($F236="","",INDEX(결산명세서!$D$5:$D$44,12))</f>
         <v/>
       </c>
       <c r="D236" s="3">
@@ -19614,7 +20240,7 @@
         <v/>
       </c>
       <c r="E236" s="22">
-        <f>IF($F236="","",INDEX(결산명세서!$H$5:$H$44,12))</f>
+        <f>IF($F236="","",INDEX(결산명세서!$I$5:$I$44,12))</f>
         <v/>
       </c>
       <c r="F236" s="23">
@@ -19980,11 +20606,11 @@
         <v/>
       </c>
       <c r="D253" s="15">
-        <f>IF($F236="","",INDEX(결산명세서!$D$5:$D$44,12))</f>
+        <f>IF($F236="","",INDEX(결산명세서!$E$5:$E$44,12))</f>
         <v/>
       </c>
       <c r="E253" s="15">
-        <f>IF($F236="","",INDEX(결산명세서!$E$5:$E$44,12))</f>
+        <f>IF($F236="","",INDEX(결산명세서!$F$5:$F$44,12))</f>
         <v/>
       </c>
     </row>
@@ -19994,11 +20620,11 @@
         <v/>
       </c>
       <c r="D254" s="15">
-        <f>IF($F236="","",INDEX(결산명세서!$F$5:$F$44,12))</f>
+        <f>IF($F236="","",INDEX(결산명세서!$G$5:$G$44,12))</f>
         <v/>
       </c>
       <c r="E254" s="15">
-        <f>IF($F236="","",INDEX(결산명세서!$G$5:$G$44,12))</f>
+        <f>IF($F236="","",INDEX(결산명세서!$H$5:$H$44,12))</f>
         <v/>
       </c>
     </row>
@@ -20019,7 +20645,7 @@
         <v/>
       </c>
       <c r="B257" s="3">
-        <f>IF($F257="","",INDEX(결산명세서!$C$5:$C$44,13))</f>
+        <f>IF($F257="","",INDEX(결산명세서!$D$5:$D$44,13))</f>
         <v/>
       </c>
       <c r="D257" s="3">
@@ -20027,7 +20653,7 @@
         <v/>
       </c>
       <c r="E257" s="22">
-        <f>IF($F257="","",INDEX(결산명세서!$H$5:$H$44,13))</f>
+        <f>IF($F257="","",INDEX(결산명세서!$I$5:$I$44,13))</f>
         <v/>
       </c>
       <c r="F257" s="23">
@@ -20393,11 +21019,11 @@
         <v/>
       </c>
       <c r="D274" s="15">
-        <f>IF($F257="","",INDEX(결산명세서!$D$5:$D$44,13))</f>
+        <f>IF($F257="","",INDEX(결산명세서!$E$5:$E$44,13))</f>
         <v/>
       </c>
       <c r="E274" s="15">
-        <f>IF($F257="","",INDEX(결산명세서!$E$5:$E$44,13))</f>
+        <f>IF($F257="","",INDEX(결산명세서!$F$5:$F$44,13))</f>
         <v/>
       </c>
     </row>
@@ -20407,11 +21033,11 @@
         <v/>
       </c>
       <c r="D275" s="15">
-        <f>IF($F257="","",INDEX(결산명세서!$F$5:$F$44,13))</f>
+        <f>IF($F257="","",INDEX(결산명세서!$G$5:$G$44,13))</f>
         <v/>
       </c>
       <c r="E275" s="15">
-        <f>IF($F257="","",INDEX(결산명세서!$G$5:$G$44,13))</f>
+        <f>IF($F257="","",INDEX(결산명세서!$H$5:$H$44,13))</f>
         <v/>
       </c>
     </row>
@@ -20432,7 +21058,7 @@
         <v/>
       </c>
       <c r="B278" s="3">
-        <f>IF($F278="","",INDEX(결산명세서!$C$5:$C$44,14))</f>
+        <f>IF($F278="","",INDEX(결산명세서!$D$5:$D$44,14))</f>
         <v/>
       </c>
       <c r="D278" s="3">
@@ -20440,7 +21066,7 @@
         <v/>
       </c>
       <c r="E278" s="22">
-        <f>IF($F278="","",INDEX(결산명세서!$H$5:$H$44,14))</f>
+        <f>IF($F278="","",INDEX(결산명세서!$I$5:$I$44,14))</f>
         <v/>
       </c>
       <c r="F278" s="23">
@@ -20806,11 +21432,11 @@
         <v/>
       </c>
       <c r="D295" s="15">
-        <f>IF($F278="","",INDEX(결산명세서!$D$5:$D$44,14))</f>
+        <f>IF($F278="","",INDEX(결산명세서!$E$5:$E$44,14))</f>
         <v/>
       </c>
       <c r="E295" s="15">
-        <f>IF($F278="","",INDEX(결산명세서!$E$5:$E$44,14))</f>
+        <f>IF($F278="","",INDEX(결산명세서!$F$5:$F$44,14))</f>
         <v/>
       </c>
     </row>
@@ -20820,11 +21446,11 @@
         <v/>
       </c>
       <c r="D296" s="15">
-        <f>IF($F278="","",INDEX(결산명세서!$F$5:$F$44,14))</f>
+        <f>IF($F278="","",INDEX(결산명세서!$G$5:$G$44,14))</f>
         <v/>
       </c>
       <c r="E296" s="15">
-        <f>IF($F278="","",INDEX(결산명세서!$G$5:$G$44,14))</f>
+        <f>IF($F278="","",INDEX(결산명세서!$H$5:$H$44,14))</f>
         <v/>
       </c>
     </row>
@@ -20845,7 +21471,7 @@
         <v/>
       </c>
       <c r="B299" s="3">
-        <f>IF($F299="","",INDEX(결산명세서!$C$5:$C$44,15))</f>
+        <f>IF($F299="","",INDEX(결산명세서!$D$5:$D$44,15))</f>
         <v/>
       </c>
       <c r="D299" s="3">
@@ -20853,7 +21479,7 @@
         <v/>
       </c>
       <c r="E299" s="22">
-        <f>IF($F299="","",INDEX(결산명세서!$H$5:$H$44,15))</f>
+        <f>IF($F299="","",INDEX(결산명세서!$I$5:$I$44,15))</f>
         <v/>
       </c>
       <c r="F299" s="23">
@@ -21219,11 +21845,11 @@
         <v/>
       </c>
       <c r="D316" s="15">
-        <f>IF($F299="","",INDEX(결산명세서!$D$5:$D$44,15))</f>
+        <f>IF($F299="","",INDEX(결산명세서!$E$5:$E$44,15))</f>
         <v/>
       </c>
       <c r="E316" s="15">
-        <f>IF($F299="","",INDEX(결산명세서!$E$5:$E$44,15))</f>
+        <f>IF($F299="","",INDEX(결산명세서!$F$5:$F$44,15))</f>
         <v/>
       </c>
     </row>
@@ -21233,11 +21859,11 @@
         <v/>
       </c>
       <c r="D317" s="15">
-        <f>IF($F299="","",INDEX(결산명세서!$F$5:$F$44,15))</f>
+        <f>IF($F299="","",INDEX(결산명세서!$G$5:$G$44,15))</f>
         <v/>
       </c>
       <c r="E317" s="15">
-        <f>IF($F299="","",INDEX(결산명세서!$G$5:$G$44,15))</f>
+        <f>IF($F299="","",INDEX(결산명세서!$H$5:$H$44,15))</f>
         <v/>
       </c>
     </row>
@@ -21258,7 +21884,7 @@
         <v/>
       </c>
       <c r="B320" s="3">
-        <f>IF($F320="","",INDEX(결산명세서!$C$5:$C$44,16))</f>
+        <f>IF($F320="","",INDEX(결산명세서!$D$5:$D$44,16))</f>
         <v/>
       </c>
       <c r="D320" s="3">
@@ -21266,7 +21892,7 @@
         <v/>
       </c>
       <c r="E320" s="22">
-        <f>IF($F320="","",INDEX(결산명세서!$H$5:$H$44,16))</f>
+        <f>IF($F320="","",INDEX(결산명세서!$I$5:$I$44,16))</f>
         <v/>
       </c>
       <c r="F320" s="23">
@@ -21632,11 +22258,11 @@
         <v/>
       </c>
       <c r="D337" s="15">
-        <f>IF($F320="","",INDEX(결산명세서!$D$5:$D$44,16))</f>
+        <f>IF($F320="","",INDEX(결산명세서!$E$5:$E$44,16))</f>
         <v/>
       </c>
       <c r="E337" s="15">
-        <f>IF($F320="","",INDEX(결산명세서!$E$5:$E$44,16))</f>
+        <f>IF($F320="","",INDEX(결산명세서!$F$5:$F$44,16))</f>
         <v/>
       </c>
     </row>
@@ -21646,11 +22272,11 @@
         <v/>
       </c>
       <c r="D338" s="15">
-        <f>IF($F320="","",INDEX(결산명세서!$F$5:$F$44,16))</f>
+        <f>IF($F320="","",INDEX(결산명세서!$G$5:$G$44,16))</f>
         <v/>
       </c>
       <c r="E338" s="15">
-        <f>IF($F320="","",INDEX(결산명세서!$G$5:$G$44,16))</f>
+        <f>IF($F320="","",INDEX(결산명세서!$H$5:$H$44,16))</f>
         <v/>
       </c>
     </row>
@@ -21671,7 +22297,7 @@
         <v/>
       </c>
       <c r="B341" s="3">
-        <f>IF($F341="","",INDEX(결산명세서!$C$5:$C$44,17))</f>
+        <f>IF($F341="","",INDEX(결산명세서!$D$5:$D$44,17))</f>
         <v/>
       </c>
       <c r="D341" s="3">
@@ -21679,7 +22305,7 @@
         <v/>
       </c>
       <c r="E341" s="22">
-        <f>IF($F341="","",INDEX(결산명세서!$H$5:$H$44,17))</f>
+        <f>IF($F341="","",INDEX(결산명세서!$I$5:$I$44,17))</f>
         <v/>
       </c>
       <c r="F341" s="23">
@@ -22045,11 +22671,11 @@
         <v/>
       </c>
       <c r="D358" s="15">
-        <f>IF($F341="","",INDEX(결산명세서!$D$5:$D$44,17))</f>
+        <f>IF($F341="","",INDEX(결산명세서!$E$5:$E$44,17))</f>
         <v/>
       </c>
       <c r="E358" s="15">
-        <f>IF($F341="","",INDEX(결산명세서!$E$5:$E$44,17))</f>
+        <f>IF($F341="","",INDEX(결산명세서!$F$5:$F$44,17))</f>
         <v/>
       </c>
     </row>
@@ -22059,11 +22685,11 @@
         <v/>
       </c>
       <c r="D359" s="15">
-        <f>IF($F341="","",INDEX(결산명세서!$F$5:$F$44,17))</f>
+        <f>IF($F341="","",INDEX(결산명세서!$G$5:$G$44,17))</f>
         <v/>
       </c>
       <c r="E359" s="15">
-        <f>IF($F341="","",INDEX(결산명세서!$G$5:$G$44,17))</f>
+        <f>IF($F341="","",INDEX(결산명세서!$H$5:$H$44,17))</f>
         <v/>
       </c>
     </row>
@@ -22084,7 +22710,7 @@
         <v/>
       </c>
       <c r="B362" s="3">
-        <f>IF($F362="","",INDEX(결산명세서!$C$5:$C$44,18))</f>
+        <f>IF($F362="","",INDEX(결산명세서!$D$5:$D$44,18))</f>
         <v/>
       </c>
       <c r="D362" s="3">
@@ -22092,7 +22718,7 @@
         <v/>
       </c>
       <c r="E362" s="22">
-        <f>IF($F362="","",INDEX(결산명세서!$H$5:$H$44,18))</f>
+        <f>IF($F362="","",INDEX(결산명세서!$I$5:$I$44,18))</f>
         <v/>
       </c>
       <c r="F362" s="23">
@@ -22458,11 +23084,11 @@
         <v/>
       </c>
       <c r="D379" s="15">
-        <f>IF($F362="","",INDEX(결산명세서!$D$5:$D$44,18))</f>
+        <f>IF($F362="","",INDEX(결산명세서!$E$5:$E$44,18))</f>
         <v/>
       </c>
       <c r="E379" s="15">
-        <f>IF($F362="","",INDEX(결산명세서!$E$5:$E$44,18))</f>
+        <f>IF($F362="","",INDEX(결산명세서!$F$5:$F$44,18))</f>
         <v/>
       </c>
     </row>
@@ -22472,11 +23098,11 @@
         <v/>
       </c>
       <c r="D380" s="15">
-        <f>IF($F362="","",INDEX(결산명세서!$F$5:$F$44,18))</f>
+        <f>IF($F362="","",INDEX(결산명세서!$G$5:$G$44,18))</f>
         <v/>
       </c>
       <c r="E380" s="15">
-        <f>IF($F362="","",INDEX(결산명세서!$G$5:$G$44,18))</f>
+        <f>IF($F362="","",INDEX(결산명세서!$H$5:$H$44,18))</f>
         <v/>
       </c>
     </row>
@@ -22497,7 +23123,7 @@
         <v/>
       </c>
       <c r="B383" s="3">
-        <f>IF($F383="","",INDEX(결산명세서!$C$5:$C$44,19))</f>
+        <f>IF($F383="","",INDEX(결산명세서!$D$5:$D$44,19))</f>
         <v/>
       </c>
       <c r="D383" s="3">
@@ -22505,7 +23131,7 @@
         <v/>
       </c>
       <c r="E383" s="22">
-        <f>IF($F383="","",INDEX(결산명세서!$H$5:$H$44,19))</f>
+        <f>IF($F383="","",INDEX(결산명세서!$I$5:$I$44,19))</f>
         <v/>
       </c>
       <c r="F383" s="23">
@@ -22871,11 +23497,11 @@
         <v/>
       </c>
       <c r="D400" s="15">
-        <f>IF($F383="","",INDEX(결산명세서!$D$5:$D$44,19))</f>
+        <f>IF($F383="","",INDEX(결산명세서!$E$5:$E$44,19))</f>
         <v/>
       </c>
       <c r="E400" s="15">
-        <f>IF($F383="","",INDEX(결산명세서!$E$5:$E$44,19))</f>
+        <f>IF($F383="","",INDEX(결산명세서!$F$5:$F$44,19))</f>
         <v/>
       </c>
     </row>
@@ -22885,11 +23511,11 @@
         <v/>
       </c>
       <c r="D401" s="15">
-        <f>IF($F383="","",INDEX(결산명세서!$F$5:$F$44,19))</f>
+        <f>IF($F383="","",INDEX(결산명세서!$G$5:$G$44,19))</f>
         <v/>
       </c>
       <c r="E401" s="15">
-        <f>IF($F383="","",INDEX(결산명세서!$G$5:$G$44,19))</f>
+        <f>IF($F383="","",INDEX(결산명세서!$H$5:$H$44,19))</f>
         <v/>
       </c>
     </row>
@@ -22910,7 +23536,7 @@
         <v/>
       </c>
       <c r="B404" s="3">
-        <f>IF($F404="","",INDEX(결산명세서!$C$5:$C$44,20))</f>
+        <f>IF($F404="","",INDEX(결산명세서!$D$5:$D$44,20))</f>
         <v/>
       </c>
       <c r="D404" s="3">
@@ -22918,7 +23544,7 @@
         <v/>
       </c>
       <c r="E404" s="22">
-        <f>IF($F404="","",INDEX(결산명세서!$H$5:$H$44,20))</f>
+        <f>IF($F404="","",INDEX(결산명세서!$I$5:$I$44,20))</f>
         <v/>
       </c>
       <c r="F404" s="23">
@@ -23284,11 +23910,11 @@
         <v/>
       </c>
       <c r="D421" s="15">
-        <f>IF($F404="","",INDEX(결산명세서!$D$5:$D$44,20))</f>
+        <f>IF($F404="","",INDEX(결산명세서!$E$5:$E$44,20))</f>
         <v/>
       </c>
       <c r="E421" s="15">
-        <f>IF($F404="","",INDEX(결산명세서!$E$5:$E$44,20))</f>
+        <f>IF($F404="","",INDEX(결산명세서!$F$5:$F$44,20))</f>
         <v/>
       </c>
     </row>
@@ -23298,11 +23924,11 @@
         <v/>
       </c>
       <c r="D422" s="15">
-        <f>IF($F404="","",INDEX(결산명세서!$F$5:$F$44,20))</f>
+        <f>IF($F404="","",INDEX(결산명세서!$G$5:$G$44,20))</f>
         <v/>
       </c>
       <c r="E422" s="15">
-        <f>IF($F404="","",INDEX(결산명세서!$G$5:$G$44,20))</f>
+        <f>IF($F404="","",INDEX(결산명세서!$H$5:$H$44,20))</f>
         <v/>
       </c>
     </row>
